--- a/distribution/reference_documents/templates/vendor process - AVCDL product mapping template.xlsx
+++ b/distribution/reference_documents/templates/vendor process - AVCDL product mapping template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charles.wilson/Documents/projects/AVCDL/source/reference_documents/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24516CA3-254C-D64A-8DAE-82FCE71A42A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59796DD-0F35-6C40-B621-E0C1EDD250DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13260" yWindow="9580" windowWidth="44220" windowHeight="27840" xr2:uid="{1C8FF072-BC4B-9747-8DA7-815499AF0FAF}"/>
+    <workbookView xWindow="13260" yWindow="9580" windowWidth="44220" windowHeight="27840" activeTab="2" xr2:uid="{1C8FF072-BC4B-9747-8DA7-815499AF0FAF}"/>
   </bookViews>
   <sheets>
     <sheet name="434 req-AVCDL product" sheetId="1" r:id="rId1"/>
@@ -107,12 +107,6 @@
     <t>deployment plan</t>
   </si>
   <si>
-    <t>product-level security goals</t>
-  </si>
-  <si>
-    <t>product-level security requirements</t>
-  </si>
-  <si>
     <t>requirements phase gate</t>
   </si>
   <si>
@@ -1044,6 +1038,12 @@
   </si>
   <si>
     <t>rev 2</t>
+  </si>
+  <si>
+    <t>element-level security goals</t>
+  </si>
+  <si>
+    <t>element-level security requirements</t>
   </si>
 </sst>
 </file>
@@ -1523,6 +1523,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1541,16 +1574,19 @@
     <xf numFmtId="1" fontId="3" fillId="4" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1647,6 +1683,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1680,69 +1743,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1765,9 +1765,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1805,7 +1805,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1911,7 +1911,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2053,7 +2053,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2093,115 +2093,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="91"/>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="68" t="s">
+      <c r="A1" s="103"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="68" t="s">
+      <c r="S1" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="68" t="s">
+      <c r="W1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="76" t="s">
+      <c r="AE1" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
-      <c r="AH1" s="77"/>
-      <c r="AI1" s="77"/>
-      <c r="AJ1" s="77"/>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
-      <c r="AN1" s="77"/>
-      <c r="AO1" s="78"/>
+      <c r="AF1" s="89"/>
+      <c r="AG1" s="89"/>
+      <c r="AH1" s="89"/>
+      <c r="AI1" s="89"/>
+      <c r="AJ1" s="89"/>
+      <c r="AK1" s="89"/>
+      <c r="AL1" s="89"/>
+      <c r="AM1" s="89"/>
+      <c r="AN1" s="89"/>
+      <c r="AO1" s="90"/>
       <c r="AP1" s="1"/>
-      <c r="AQ1" s="79" t="s">
+      <c r="AQ1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="80"/>
-      <c r="AS1" s="80"/>
-      <c r="AT1" s="81"/>
+      <c r="AR1" s="92"/>
+      <c r="AS1" s="92"/>
+      <c r="AT1" s="93"/>
       <c r="AU1" s="1"/>
-      <c r="AV1" s="68" t="s">
+      <c r="AV1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="AW1" s="68"/>
-      <c r="AX1" s="68"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
       <c r="AY1" s="1"/>
-      <c r="AZ1" s="65" t="s">
+      <c r="AZ1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="BA1" s="66"/>
-      <c r="BB1" s="66"/>
-      <c r="BC1" s="67"/>
+      <c r="BA1" s="77"/>
+      <c r="BB1" s="77"/>
+      <c r="BC1" s="78"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="BF1" s="1"/>
-      <c r="BG1" s="68" t="s">
+      <c r="BG1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="BH1" s="68"/>
-      <c r="BI1" s="68"/>
+      <c r="BH1" s="79"/>
+      <c r="BI1" s="79"/>
     </row>
     <row r="2" spans="1:61" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="91"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="69">
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="80">
         <v>1</v>
       </c>
-      <c r="F2" s="70"/>
+      <c r="F2" s="81"/>
       <c r="G2" s="3">
         <v>2</v>
       </c>
       <c r="H2" s="3">
         <v>3</v>
       </c>
-      <c r="I2" s="138">
+      <c r="I2" s="82">
         <v>4</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="81"/>
       <c r="K2" s="4">
         <v>5</v>
       </c>
       <c r="L2" s="3">
         <v>6</v>
       </c>
-      <c r="M2" s="73">
+      <c r="M2" s="83">
         <v>7</v>
       </c>
-      <c r="N2" s="74"/>
+      <c r="N2" s="84"/>
       <c r="O2" s="3">
         <v>8</v>
       </c>
@@ -2212,10 +2212,10 @@
         <v>10</v>
       </c>
       <c r="R2" s="5"/>
-      <c r="S2" s="71">
+      <c r="S2" s="85">
         <v>1</v>
       </c>
-      <c r="T2" s="72"/>
+      <c r="T2" s="86"/>
       <c r="U2" s="6">
         <v>2</v>
       </c>
@@ -2229,11 +2229,11 @@
       <c r="Y2" s="4">
         <v>3</v>
       </c>
-      <c r="Z2" s="75">
+      <c r="Z2" s="87">
         <v>4</v>
       </c>
-      <c r="AA2" s="75"/>
-      <c r="AB2" s="75"/>
+      <c r="AA2" s="87"/>
+      <c r="AB2" s="87"/>
       <c r="AC2" s="6">
         <v>5</v>
       </c>
@@ -2323,10 +2323,10 @@
       </c>
     </row>
     <row r="3" spans="1:61" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="91"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="92"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="10">
         <v>1</v>
       </c>
@@ -2484,10 +2484,10 @@
       </c>
     </row>
     <row r="4" spans="1:61" s="20" customFormat="1" ht="329" x14ac:dyDescent="0.2">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="92"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
       <c r="E4" s="16" t="s">
         <v>10</v>
       </c>
@@ -2529,129 +2529,129 @@
       </c>
       <c r="R4" s="18"/>
       <c r="S4" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="U4" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U4" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="V4" s="18"/>
       <c r="W4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="19" t="s">
+      <c r="Z4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="19" t="s">
+      <c r="AA4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="19" t="s">
+      <c r="AB4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AC4" s="19" t="s">
         <v>30</v>
-      </c>
-      <c r="AB4" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC4" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="AD4" s="18"/>
       <c r="AE4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AF4" s="19" t="s">
+      <c r="AH4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AG4" s="19" t="s">
+      <c r="AI4" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="19" t="s">
+      <c r="AK4" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AJ4" s="19" t="s">
+      <c r="AL4" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="19" t="s">
+      <c r="AM4" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AL4" s="19" t="s">
+      <c r="AN4" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AM4" s="19" t="s">
+      <c r="AO4" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="AN4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO4" s="19" t="s">
-        <v>43</v>
       </c>
       <c r="AP4" s="18"/>
       <c r="AQ4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS4" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AR4" s="19" t="s">
+      <c r="AT4" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="AS4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT4" s="19" t="s">
-        <v>47</v>
       </c>
       <c r="AU4" s="18"/>
       <c r="AV4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AW4" s="19" t="s">
+      <c r="AY4" s="18"/>
+      <c r="AZ4" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="AX4" s="19" t="s">
+      <c r="BA4" s="106"/>
+      <c r="BB4" s="107"/>
+      <c r="BC4" s="19" t="s">
         <v>50</v>
-      </c>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="93" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA4" s="94"/>
-      <c r="BB4" s="95"/>
-      <c r="BC4" s="19" t="s">
-        <v>52</v>
       </c>
       <c r="BD4" s="18"/>
       <c r="BE4" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="BF4" s="18"/>
       <c r="BG4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="BH4" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="BI4" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="BH4" s="19" t="s">
+    </row>
+    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A5" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="BI4" s="19" t="s">
+      <c r="B5" s="97" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A5" s="82" t="s">
+      <c r="C5" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="85" t="s">
+      <c r="D5" s="22" t="s">
         <v>58</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>60</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="24"/>
@@ -2712,13 +2712,13 @@
       <c r="BI5" s="25"/>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A6" s="83"/>
-      <c r="B6" s="86"/>
+      <c r="A6" s="95"/>
+      <c r="B6" s="98"/>
       <c r="C6" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="24"/>
@@ -2779,13 +2779,13 @@
       <c r="BI6" s="25"/>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A7" s="83"/>
-      <c r="B7" s="86"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="98"/>
       <c r="C7" s="27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="24"/>
@@ -2848,13 +2848,13 @@
       <c r="BI7" s="25"/>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A8" s="83"/>
-      <c r="B8" s="86"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="24"/>
@@ -2915,13 +2915,13 @@
       <c r="BI8" s="25"/>
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A9" s="83"/>
-      <c r="B9" s="86"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
@@ -2982,13 +2982,13 @@
       <c r="BI9" s="25"/>
     </row>
     <row r="10" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A10" s="83"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="95"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
@@ -3049,13 +3049,13 @@
       <c r="BI10" s="24"/>
     </row>
     <row r="11" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A11" s="83"/>
-      <c r="B11" s="86"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="98"/>
       <c r="C11" s="27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>9</v>
@@ -3120,13 +3120,13 @@
       <c r="BI11" s="24"/>
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A12" s="83"/>
-      <c r="B12" s="86"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="98"/>
       <c r="C12" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
@@ -3187,13 +3187,13 @@
       <c r="BI12" s="24"/>
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A13" s="83"/>
-      <c r="B13" s="87"/>
+      <c r="A13" s="95"/>
+      <c r="B13" s="99"/>
       <c r="C13" s="21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="24"/>
@@ -3254,15 +3254,15 @@
       <c r="BI13" s="25"/>
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A14" s="83"/>
-      <c r="B14" s="85" t="s">
-        <v>77</v>
+      <c r="A14" s="95"/>
+      <c r="B14" s="97" t="s">
+        <v>75</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>9</v>
@@ -3327,13 +3327,13 @@
       <c r="BI14" s="24"/>
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A15" s="83"/>
-      <c r="B15" s="87"/>
+      <c r="A15" s="95"/>
+      <c r="B15" s="99"/>
       <c r="C15" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="24"/>
@@ -3394,15 +3394,15 @@
       <c r="BI15" s="24"/>
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A16" s="83"/>
-      <c r="B16" s="85" t="s">
+      <c r="A16" s="95"/>
+      <c r="B16" s="97" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>78</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>80</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="24"/>
@@ -3463,13 +3463,13 @@
       <c r="BI16" s="24"/>
     </row>
     <row r="17" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A17" s="83"/>
-      <c r="B17" s="86"/>
+      <c r="A17" s="95"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="24"/>
@@ -3530,15 +3530,15 @@
       <c r="BI17" s="24"/>
     </row>
     <row r="18" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A18" s="83"/>
+      <c r="A18" s="95"/>
       <c r="B18" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>85</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="24"/>
@@ -3603,15 +3603,15 @@
       <c r="BI18" s="24"/>
     </row>
     <row r="19" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A19" s="84"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>86</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>88</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="24"/>
@@ -3672,17 +3672,17 @@
       <c r="BI19" s="24"/>
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="85" t="s">
+      <c r="D20" s="22" t="s">
         <v>90</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>92</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="24"/>
@@ -3745,13 +3745,13 @@
       <c r="BI20" s="24"/>
     </row>
     <row r="21" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A21" s="83"/>
-      <c r="B21" s="86"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E21" s="23"/>
       <c r="F21" s="24"/>
@@ -3812,13 +3812,13 @@
       <c r="BI21" s="24"/>
     </row>
     <row r="22" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A22" s="83"/>
-      <c r="B22" s="86"/>
+      <c r="A22" s="95"/>
+      <c r="B22" s="98"/>
       <c r="C22" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E22" s="23"/>
       <c r="F22" s="24"/>
@@ -3879,13 +3879,13 @@
       <c r="BI22" s="24"/>
     </row>
     <row r="23" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A23" s="83"/>
-      <c r="B23" s="86"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>95</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>97</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="24"/>
@@ -3948,13 +3948,13 @@
       <c r="BI23" s="24"/>
     </row>
     <row r="24" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A24" s="83"/>
-      <c r="B24" s="86"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" s="23"/>
       <c r="F24" s="24"/>
@@ -4015,13 +4015,13 @@
       <c r="BI24" s="24"/>
     </row>
     <row r="25" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A25" s="83"/>
-      <c r="B25" s="86"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
@@ -4082,13 +4082,13 @@
       <c r="BI25" s="24"/>
     </row>
     <row r="26" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A26" s="83"/>
-      <c r="B26" s="86"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="98"/>
       <c r="C26" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -4149,13 +4149,13 @@
       <c r="BI26" s="24"/>
     </row>
     <row r="27" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A27" s="83"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="98"/>
       <c r="C27" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="24"/>
@@ -4216,13 +4216,13 @@
       <c r="BI27" s="24"/>
     </row>
     <row r="28" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A28" s="83"/>
-      <c r="B28" s="86"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E28" s="23"/>
       <c r="F28" s="24"/>
@@ -4283,13 +4283,13 @@
       <c r="BI28" s="24"/>
     </row>
     <row r="29" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A29" s="83"/>
-      <c r="B29" s="86"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="24"/>
@@ -4350,13 +4350,13 @@
       <c r="BI29" s="24"/>
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A30" s="83"/>
-      <c r="B30" s="86"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="98"/>
       <c r="C30" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E30" s="23"/>
       <c r="F30" s="24"/>
@@ -4417,13 +4417,13 @@
       <c r="BI30" s="24"/>
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A31" s="83"/>
-      <c r="B31" s="86"/>
+      <c r="A31" s="95"/>
+      <c r="B31" s="98"/>
       <c r="C31" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E31" s="23"/>
       <c r="F31" s="24"/>
@@ -4484,13 +4484,13 @@
       <c r="BI31" s="24"/>
     </row>
     <row r="32" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A32" s="83"/>
-      <c r="B32" s="86"/>
+      <c r="A32" s="95"/>
+      <c r="B32" s="98"/>
       <c r="C32" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" s="23"/>
       <c r="F32" s="24"/>
@@ -4551,13 +4551,13 @@
       <c r="BI32" s="24"/>
     </row>
     <row r="33" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A33" s="83"/>
-      <c r="B33" s="86"/>
+      <c r="A33" s="95"/>
+      <c r="B33" s="98"/>
       <c r="C33" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E33" s="23"/>
       <c r="F33" s="24"/>
@@ -4618,13 +4618,13 @@
       <c r="BI33" s="24"/>
     </row>
     <row r="34" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A34" s="83"/>
-      <c r="B34" s="86"/>
+      <c r="A34" s="95"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E34" s="23"/>
       <c r="F34" s="24"/>
@@ -4685,13 +4685,13 @@
       <c r="BI34" s="24"/>
     </row>
     <row r="35" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A35" s="83"/>
-      <c r="B35" s="86"/>
+      <c r="A35" s="95"/>
+      <c r="B35" s="98"/>
       <c r="C35" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E35" s="23"/>
       <c r="F35" s="24"/>
@@ -4752,13 +4752,13 @@
       <c r="BI35" s="24"/>
     </row>
     <row r="36" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A36" s="83"/>
-      <c r="B36" s="86"/>
+      <c r="A36" s="95"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E36" s="23"/>
       <c r="F36" s="24"/>
@@ -4819,13 +4819,13 @@
       <c r="BI36" s="24"/>
     </row>
     <row r="37" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A37" s="83"/>
-      <c r="B37" s="86"/>
+      <c r="A37" s="95"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -4886,13 +4886,13 @@
       <c r="BI37" s="24"/>
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A38" s="83"/>
-      <c r="B38" s="86"/>
+      <c r="A38" s="95"/>
+      <c r="B38" s="98"/>
       <c r="C38" s="21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E38" s="23"/>
       <c r="F38" s="24"/>
@@ -4953,13 +4953,13 @@
       <c r="BI38" s="24"/>
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A39" s="83"/>
-      <c r="B39" s="87"/>
+      <c r="A39" s="95"/>
+      <c r="B39" s="99"/>
       <c r="C39" s="21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="24"/>
@@ -5020,15 +5020,15 @@
       <c r="BI39" s="24"/>
     </row>
     <row r="40" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A40" s="83"/>
+      <c r="A40" s="95"/>
       <c r="B40" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="22" t="s">
         <v>130</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>132</v>
       </c>
       <c r="E40" s="23"/>
       <c r="F40" s="24"/>
@@ -5089,15 +5089,15 @@
       <c r="BI40" s="24"/>
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A41" s="83"/>
-      <c r="B41" s="88" t="s">
+      <c r="A41" s="95"/>
+      <c r="B41" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>135</v>
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
@@ -5160,13 +5160,13 @@
       <c r="BI41" s="24"/>
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A42" s="83"/>
-      <c r="B42" s="89"/>
+      <c r="A42" s="95"/>
+      <c r="B42" s="101"/>
       <c r="C42" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E42" s="23"/>
       <c r="F42" s="24"/>
@@ -5229,13 +5229,13 @@
       <c r="BI42" s="24"/>
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A43" s="83"/>
-      <c r="B43" s="89"/>
+      <c r="A43" s="95"/>
+      <c r="B43" s="101"/>
       <c r="C43" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -5298,13 +5298,13 @@
       <c r="BI43" s="24"/>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A44" s="83"/>
-      <c r="B44" s="89"/>
+      <c r="A44" s="95"/>
+      <c r="B44" s="101"/>
       <c r="C44" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E44" s="23"/>
       <c r="F44" s="24"/>
@@ -5367,13 +5367,13 @@
       <c r="BI44" s="24"/>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A45" s="83"/>
-      <c r="B45" s="89"/>
+      <c r="A45" s="95"/>
+      <c r="B45" s="101"/>
       <c r="C45" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="24"/>
@@ -5436,13 +5436,13 @@
       <c r="BI45" s="24"/>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A46" s="83"/>
-      <c r="B46" s="89"/>
+      <c r="A46" s="95"/>
+      <c r="B46" s="101"/>
       <c r="C46" s="30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E46" s="23"/>
       <c r="F46" s="24"/>
@@ -5505,13 +5505,13 @@
       <c r="BI46" s="24"/>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A47" s="83"/>
-      <c r="B47" s="89"/>
+      <c r="A47" s="95"/>
+      <c r="B47" s="101"/>
       <c r="C47" s="30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E47" s="23"/>
       <c r="F47" s="24"/>
@@ -5574,13 +5574,13 @@
       <c r="BI47" s="24"/>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A48" s="83"/>
-      <c r="B48" s="90"/>
+      <c r="A48" s="95"/>
+      <c r="B48" s="102"/>
       <c r="C48" s="30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -5643,15 +5643,15 @@
       <c r="BI48" s="24"/>
     </row>
     <row r="49" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A49" s="83"/>
-      <c r="B49" s="88" t="s">
+      <c r="A49" s="95"/>
+      <c r="B49" s="100" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>152</v>
       </c>
       <c r="E49" s="23"/>
       <c r="F49" s="24"/>
@@ -5716,13 +5716,13 @@
       <c r="BI49" s="24"/>
     </row>
     <row r="50" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A50" s="84"/>
-      <c r="B50" s="90"/>
+      <c r="A50" s="96"/>
+      <c r="B50" s="102"/>
       <c r="C50" s="30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E50" s="23"/>
       <c r="F50" s="24"/>
@@ -5850,17 +5850,17 @@
       <c r="BI51" s="26"/>
     </row>
     <row r="52" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="108" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="111" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B52" s="99" t="s">
+      <c r="D52" s="22" t="s">
         <v>156</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>158</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -5925,13 +5925,13 @@
       <c r="BI52" s="24"/>
     </row>
     <row r="53" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A53" s="98"/>
-      <c r="B53" s="100"/>
+      <c r="A53" s="110"/>
+      <c r="B53" s="112"/>
       <c r="C53" s="30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E53" s="23"/>
       <c r="F53" s="24"/>
@@ -5996,15 +5996,15 @@
       <c r="BI53" s="24"/>
     </row>
     <row r="54" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A54" s="98"/>
+      <c r="A54" s="110"/>
       <c r="B54" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="22" t="s">
         <v>161</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>163</v>
       </c>
       <c r="E54" s="23"/>
       <c r="F54" s="24"/>
@@ -6065,15 +6065,15 @@
       <c r="BI54" s="24"/>
     </row>
     <row r="55" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A55" s="98"/>
-      <c r="B55" s="88" t="s">
+      <c r="A55" s="110"/>
+      <c r="B55" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="22" t="s">
         <v>164</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>166</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="24"/>
@@ -6136,13 +6136,13 @@
       </c>
     </row>
     <row r="56" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A56" s="98"/>
-      <c r="B56" s="89"/>
+      <c r="A56" s="110"/>
+      <c r="B56" s="101"/>
       <c r="C56" s="30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="24"/>
@@ -6205,13 +6205,13 @@
       </c>
     </row>
     <row r="57" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A57" s="97"/>
-      <c r="B57" s="90"/>
+      <c r="A57" s="109"/>
+      <c r="B57" s="102"/>
       <c r="C57" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="24"/>
@@ -6337,17 +6337,17 @@
       <c r="BI58" s="26"/>
     </row>
     <row r="59" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A59" s="96" t="s">
+      <c r="A59" s="108" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="B59" s="40" t="s">
+      <c r="D59" s="22" t="s">
         <v>172</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>174</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="24"/>
@@ -6410,15 +6410,15 @@
       <c r="BI59" s="24"/>
     </row>
     <row r="60" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A60" s="98"/>
+      <c r="A60" s="110"/>
       <c r="B60" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="22" t="s">
         <v>175</v>
-      </c>
-      <c r="C60" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>177</v>
       </c>
       <c r="E60" s="23"/>
       <c r="F60" s="24"/>
@@ -6481,15 +6481,15 @@
       <c r="BI60" s="24"/>
     </row>
     <row r="61" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A61" s="98"/>
+      <c r="A61" s="110"/>
       <c r="B61" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="22" t="s">
         <v>178</v>
-      </c>
-      <c r="C61" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>180</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="24"/>
@@ -6554,15 +6554,15 @@
       <c r="BI61" s="24"/>
     </row>
     <row r="62" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A62" s="98"/>
+      <c r="A62" s="110"/>
       <c r="B62" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" s="22" t="s">
         <v>181</v>
-      </c>
-      <c r="C62" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>183</v>
       </c>
       <c r="E62" s="23"/>
       <c r="F62" s="24"/>
@@ -6627,15 +6627,15 @@
       <c r="BI62" s="24"/>
     </row>
     <row r="63" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A63" s="98"/>
-      <c r="B63" s="88" t="s">
+      <c r="A63" s="110"/>
+      <c r="B63" s="100" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" s="22" t="s">
         <v>184</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>186</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="24"/>
@@ -6702,13 +6702,13 @@
       <c r="BI63" s="24"/>
     </row>
     <row r="64" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A64" s="98"/>
-      <c r="B64" s="90"/>
+      <c r="A64" s="110"/>
+      <c r="B64" s="102"/>
       <c r="C64" s="30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="24"/>
@@ -6775,15 +6775,15 @@
       <c r="BI64" s="24"/>
     </row>
     <row r="65" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A65" s="98"/>
+      <c r="A65" s="110"/>
       <c r="B65" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="D65" s="22" t="s">
         <v>189</v>
-      </c>
-      <c r="C65" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>191</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="24"/>
@@ -6856,15 +6856,15 @@
       <c r="BI65" s="24"/>
     </row>
     <row r="66" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A66" s="97"/>
+      <c r="A66" s="109"/>
       <c r="B66" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="22" t="s">
         <v>192</v>
-      </c>
-      <c r="C66" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>194</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="24"/>
@@ -6996,17 +6996,17 @@
       <c r="BI67" s="26"/>
     </row>
     <row r="68" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A68" s="96" t="s">
+      <c r="A68" s="108" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="113" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="B68" s="101" t="s">
+      <c r="D68" s="22" t="s">
         <v>196</v>
-      </c>
-      <c r="C68" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>198</v>
       </c>
       <c r="E68" s="23"/>
       <c r="F68" s="24"/>
@@ -7071,13 +7071,13 @@
       <c r="BI68" s="24"/>
     </row>
     <row r="69" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A69" s="98"/>
-      <c r="B69" s="101"/>
+      <c r="A69" s="110"/>
+      <c r="B69" s="113"/>
       <c r="C69" s="30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E69" s="23"/>
       <c r="F69" s="24"/>
@@ -7142,15 +7142,15 @@
       <c r="BI69" s="24"/>
     </row>
     <row r="70" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A70" s="98"/>
-      <c r="B70" s="101" t="s">
+      <c r="A70" s="110"/>
+      <c r="B70" s="113" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" s="22" t="s">
         <v>201</v>
-      </c>
-      <c r="C70" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>203</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="24"/>
@@ -7213,13 +7213,13 @@
       <c r="BI70" s="24"/>
     </row>
     <row r="71" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A71" s="98"/>
-      <c r="B71" s="101"/>
+      <c r="A71" s="110"/>
+      <c r="B71" s="113"/>
       <c r="C71" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E71" s="23"/>
       <c r="F71" s="24"/>
@@ -7284,15 +7284,15 @@
       <c r="BI71" s="24"/>
     </row>
     <row r="72" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A72" s="98"/>
+      <c r="A72" s="110"/>
       <c r="B72" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72" s="22" t="s">
         <v>206</v>
-      </c>
-      <c r="C72" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>208</v>
       </c>
       <c r="E72" s="23"/>
       <c r="F72" s="24"/>
@@ -7355,15 +7355,15 @@
       <c r="BI72" s="24"/>
     </row>
     <row r="73" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A73" s="98"/>
+      <c r="A73" s="110"/>
       <c r="B73" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D73" s="22" t="s">
         <v>209</v>
-      </c>
-      <c r="C73" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>211</v>
       </c>
       <c r="E73" s="23"/>
       <c r="F73" s="24"/>
@@ -7426,15 +7426,15 @@
       <c r="BI73" s="24"/>
     </row>
     <row r="74" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A74" s="98"/>
+      <c r="A74" s="110"/>
       <c r="B74" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D74" s="22" t="s">
         <v>212</v>
-      </c>
-      <c r="C74" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>214</v>
       </c>
       <c r="E74" s="23"/>
       <c r="F74" s="24"/>
@@ -7497,15 +7497,15 @@
       <c r="BI74" s="24"/>
     </row>
     <row r="75" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A75" s="98"/>
-      <c r="B75" s="101" t="s">
+      <c r="A75" s="110"/>
+      <c r="B75" s="113" t="s">
+        <v>213</v>
+      </c>
+      <c r="C75" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="D75" s="22" t="s">
         <v>215</v>
-      </c>
-      <c r="C75" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="24"/>
@@ -7568,13 +7568,13 @@
       <c r="BI75" s="24"/>
     </row>
     <row r="76" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A76" s="98"/>
-      <c r="B76" s="101"/>
+      <c r="A76" s="110"/>
+      <c r="B76" s="113"/>
       <c r="C76" s="44" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D76" s="22" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
@@ -7637,13 +7637,13 @@
       <c r="BI76" s="24"/>
     </row>
     <row r="77" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A77" s="98"/>
-      <c r="B77" s="101"/>
+      <c r="A77" s="110"/>
+      <c r="B77" s="113"/>
       <c r="C77" s="44" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="24"/>
@@ -7706,15 +7706,15 @@
       <c r="BI77" s="24"/>
     </row>
     <row r="78" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A78" s="97"/>
+      <c r="A78" s="109"/>
       <c r="B78" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="D78" s="22" t="s">
         <v>222</v>
-      </c>
-      <c r="C78" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="D78" s="22" t="s">
-        <v>224</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="24"/>
@@ -7777,17 +7777,17 @@
       <c r="BI78" s="24"/>
     </row>
     <row r="79" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A79" s="96" t="s">
+      <c r="A79" s="108" t="s">
+        <v>223</v>
+      </c>
+      <c r="B79" s="100" t="s">
+        <v>224</v>
+      </c>
+      <c r="C79" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="B79" s="88" t="s">
+      <c r="D79" s="22" t="s">
         <v>226</v>
-      </c>
-      <c r="C79" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>228</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="24"/>
@@ -7850,13 +7850,13 @@
       <c r="BI79" s="24"/>
     </row>
     <row r="80" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A80" s="98"/>
-      <c r="B80" s="90"/>
+      <c r="A80" s="110"/>
+      <c r="B80" s="102"/>
       <c r="C80" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E80" s="23"/>
       <c r="F80" s="24"/>
@@ -7919,15 +7919,15 @@
       <c r="BI80" s="24"/>
     </row>
     <row r="81" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A81" s="98"/>
+      <c r="A81" s="110"/>
       <c r="B81" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="D81" s="22" t="s">
         <v>231</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="D81" s="22" t="s">
-        <v>233</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="24"/>
@@ -7990,15 +7990,15 @@
       <c r="BI81" s="24"/>
     </row>
     <row r="82" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A82" s="98"/>
-      <c r="B82" s="101" t="s">
+      <c r="A82" s="110"/>
+      <c r="B82" s="113" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="D82" s="22" t="s">
         <v>234</v>
-      </c>
-      <c r="C82" s="44" t="s">
-        <v>235</v>
-      </c>
-      <c r="D82" s="22" t="s">
-        <v>236</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="24"/>
@@ -8061,13 +8061,13 @@
       <c r="BI82" s="24"/>
     </row>
     <row r="83" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A83" s="98"/>
-      <c r="B83" s="101"/>
+      <c r="A83" s="110"/>
+      <c r="B83" s="113"/>
       <c r="C83" s="44" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="24"/>
@@ -8130,15 +8130,15 @@
       <c r="BI83" s="24"/>
     </row>
     <row r="84" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A84" s="98"/>
+      <c r="A84" s="110"/>
       <c r="B84" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="D84" s="22" t="s">
         <v>239</v>
-      </c>
-      <c r="C84" s="44" t="s">
-        <v>240</v>
-      </c>
-      <c r="D84" s="22" t="s">
-        <v>241</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="24"/>
@@ -8203,15 +8203,15 @@
       <c r="BI84" s="24"/>
     </row>
     <row r="85" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A85" s="98"/>
-      <c r="B85" s="88" t="s">
+      <c r="A85" s="110"/>
+      <c r="B85" s="100" t="s">
+        <v>240</v>
+      </c>
+      <c r="C85" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="22" t="s">
         <v>242</v>
-      </c>
-      <c r="C85" s="44" t="s">
-        <v>243</v>
-      </c>
-      <c r="D85" s="22" t="s">
-        <v>244</v>
       </c>
       <c r="E85" s="23"/>
       <c r="F85" s="24"/>
@@ -8276,13 +8276,13 @@
       <c r="BI85" s="24"/>
     </row>
     <row r="86" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A86" s="98"/>
-      <c r="B86" s="89"/>
+      <c r="A86" s="110"/>
+      <c r="B86" s="101"/>
       <c r="C86" s="44" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E86" s="23"/>
       <c r="F86" s="24"/>
@@ -8347,13 +8347,13 @@
       <c r="BI86" s="24"/>
     </row>
     <row r="87" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A87" s="98"/>
-      <c r="B87" s="90"/>
+      <c r="A87" s="110"/>
+      <c r="B87" s="102"/>
       <c r="C87" s="44" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="24"/>
@@ -8418,15 +8418,15 @@
       <c r="BI87" s="24"/>
     </row>
     <row r="88" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A88" s="98"/>
+      <c r="A88" s="110"/>
       <c r="B88" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="D88" s="22" t="s">
         <v>249</v>
-      </c>
-      <c r="C88" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="D88" s="22" t="s">
-        <v>251</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="24"/>
@@ -8493,15 +8493,15 @@
       <c r="BI88" s="24"/>
     </row>
     <row r="89" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A89" s="98"/>
-      <c r="B89" s="88" t="s">
+      <c r="A89" s="110"/>
+      <c r="B89" s="100" t="s">
+        <v>250</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="22" t="s">
         <v>252</v>
-      </c>
-      <c r="C89" s="44" t="s">
-        <v>253</v>
-      </c>
-      <c r="D89" s="22" t="s">
-        <v>254</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="24"/>
@@ -8566,13 +8566,13 @@
       <c r="BI89" s="24"/>
     </row>
     <row r="90" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A90" s="98"/>
-      <c r="B90" s="89"/>
+      <c r="A90" s="110"/>
+      <c r="B90" s="101"/>
       <c r="C90" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="24"/>
@@ -8637,13 +8637,13 @@
       <c r="BI90" s="24"/>
     </row>
     <row r="91" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A91" s="98"/>
-      <c r="B91" s="89"/>
+      <c r="A91" s="110"/>
+      <c r="B91" s="101"/>
       <c r="C91" s="44" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
@@ -8708,13 +8708,13 @@
       <c r="BI91" s="24"/>
     </row>
     <row r="92" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A92" s="97"/>
-      <c r="B92" s="90"/>
+      <c r="A92" s="109"/>
+      <c r="B92" s="102"/>
       <c r="C92" s="44" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="24"/>
@@ -8779,17 +8779,17 @@
       <c r="BI92" s="24"/>
     </row>
     <row r="93" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A93" s="96" t="s">
+      <c r="A93" s="108" t="s">
+        <v>255</v>
+      </c>
+      <c r="B93" s="100" t="s">
+        <v>256</v>
+      </c>
+      <c r="C93" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="B93" s="88" t="s">
+      <c r="D93" s="22" t="s">
         <v>258</v>
-      </c>
-      <c r="C93" s="44" t="s">
-        <v>259</v>
-      </c>
-      <c r="D93" s="22" t="s">
-        <v>260</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="24"/>
@@ -8852,13 +8852,13 @@
       <c r="BI93" s="24"/>
     </row>
     <row r="94" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A94" s="97"/>
-      <c r="B94" s="90"/>
+      <c r="A94" s="109"/>
+      <c r="B94" s="102"/>
       <c r="C94" s="44" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
@@ -8984,17 +8984,17 @@
       <c r="BI95" s="26"/>
     </row>
     <row r="96" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A96" s="96" t="s">
+      <c r="A96" s="108" t="s">
+        <v>261</v>
+      </c>
+      <c r="B96" s="113" t="s">
+        <v>262</v>
+      </c>
+      <c r="C96" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="B96" s="101" t="s">
+      <c r="D96" s="22" t="s">
         <v>264</v>
-      </c>
-      <c r="C96" s="44" t="s">
-        <v>265</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>266</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="24"/>
@@ -9059,13 +9059,13 @@
       <c r="BI96" s="24"/>
     </row>
     <row r="97" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A97" s="98"/>
-      <c r="B97" s="101"/>
+      <c r="A97" s="110"/>
+      <c r="B97" s="113"/>
       <c r="C97" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="24"/>
@@ -9130,15 +9130,15 @@
       <c r="BI97" s="24"/>
     </row>
     <row r="98" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="97"/>
+      <c r="A98" s="109"/>
       <c r="B98" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="C98" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="D98" s="22" t="s">
         <v>269</v>
-      </c>
-      <c r="C98" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>271</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="24"/>
@@ -9200,17 +9200,17 @@
       <c r="BI98" s="24"/>
     </row>
     <row r="99" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A99" s="96" t="s">
+      <c r="A99" s="108" t="s">
+        <v>270</v>
+      </c>
+      <c r="B99" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="C99" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="B99" s="45" t="s">
+      <c r="D99" s="22" t="s">
         <v>273</v>
-      </c>
-      <c r="C99" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="D99" s="22" t="s">
-        <v>275</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="24"/>
@@ -9273,15 +9273,15 @@
       <c r="BI99" s="24"/>
     </row>
     <row r="100" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A100" s="98"/>
+      <c r="A100" s="110"/>
       <c r="B100" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="C100" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="D100" s="22" t="s">
         <v>276</v>
-      </c>
-      <c r="C100" s="44" t="s">
-        <v>277</v>
-      </c>
-      <c r="D100" s="22" t="s">
-        <v>278</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="24"/>
@@ -9348,15 +9348,15 @@
       <c r="BI100" s="24"/>
     </row>
     <row r="101" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="97"/>
+      <c r="A101" s="109"/>
       <c r="B101" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="C101" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="D101" s="46" t="s">
         <v>279</v>
-      </c>
-      <c r="C101" s="44" t="s">
-        <v>280</v>
-      </c>
-      <c r="D101" s="46" t="s">
-        <v>281</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="24"/>
@@ -9418,17 +9418,17 @@
       <c r="BI101" s="24"/>
     </row>
     <row r="102" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="96" t="s">
+      <c r="A102" s="108" t="s">
+        <v>280</v>
+      </c>
+      <c r="B102" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="C102" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="B102" s="40" t="s">
+      <c r="D102" s="46" t="s">
         <v>283</v>
-      </c>
-      <c r="C102" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="D102" s="46" t="s">
-        <v>285</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="24"/>
@@ -9491,15 +9491,15 @@
       <c r="BI102" s="24"/>
     </row>
     <row r="103" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A103" s="97"/>
+      <c r="A103" s="109"/>
       <c r="B103" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="D103" s="22" t="s">
         <v>286</v>
-      </c>
-      <c r="C103" s="44" t="s">
-        <v>287</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>288</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="24"/>
@@ -9625,17 +9625,17 @@
       <c r="BI104" s="26"/>
     </row>
     <row r="105" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A105" s="96" t="s">
+      <c r="A105" s="108" t="s">
+        <v>287</v>
+      </c>
+      <c r="B105" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C105" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B105" s="40" t="s">
+      <c r="D105" s="22" t="s">
         <v>290</v>
-      </c>
-      <c r="C105" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D105" s="22" t="s">
-        <v>292</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="24"/>
@@ -9698,15 +9698,15 @@
       <c r="BI105" s="24"/>
     </row>
     <row r="106" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A106" s="98"/>
+      <c r="A106" s="110"/>
       <c r="B106" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="C106" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="D106" s="22" t="s">
         <v>293</v>
-      </c>
-      <c r="C106" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D106" s="22" t="s">
-        <v>295</v>
       </c>
       <c r="E106" s="23"/>
       <c r="F106" s="24"/>
@@ -9769,15 +9769,15 @@
       <c r="BI106" s="24"/>
     </row>
     <row r="107" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A107" s="98"/>
+      <c r="A107" s="110"/>
       <c r="B107" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="C107" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="D107" s="22" t="s">
         <v>296</v>
-      </c>
-      <c r="C107" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="D107" s="22" t="s">
-        <v>298</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="24"/>
@@ -9840,15 +9840,15 @@
       <c r="BI107" s="24"/>
     </row>
     <row r="108" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A108" s="98"/>
-      <c r="B108" s="101" t="s">
+      <c r="A108" s="110"/>
+      <c r="B108" s="113" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="D108" s="22" t="s">
         <v>299</v>
-      </c>
-      <c r="C108" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="D108" s="22" t="s">
-        <v>301</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="24"/>
@@ -9911,13 +9911,13 @@
       <c r="BI108" s="24"/>
     </row>
     <row r="109" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A109" s="98"/>
-      <c r="B109" s="101"/>
+      <c r="A109" s="110"/>
+      <c r="B109" s="113"/>
       <c r="C109" s="44" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E109" s="23"/>
       <c r="F109" s="24"/>
@@ -9980,13 +9980,13 @@
       <c r="BI109" s="24"/>
     </row>
     <row r="110" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A110" s="98"/>
-      <c r="B110" s="101"/>
+      <c r="A110" s="110"/>
+      <c r="B110" s="113"/>
       <c r="C110" s="44" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="24"/>
@@ -10049,15 +10049,15 @@
       <c r="BI110" s="24"/>
     </row>
     <row r="111" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A111" s="98"/>
-      <c r="B111" s="101" t="s">
+      <c r="A111" s="110"/>
+      <c r="B111" s="113" t="s">
+        <v>304</v>
+      </c>
+      <c r="C111" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="D111" s="22" t="s">
         <v>306</v>
-      </c>
-      <c r="C111" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="D111" s="22" t="s">
-        <v>308</v>
       </c>
       <c r="E111" s="23"/>
       <c r="F111" s="24"/>
@@ -10120,13 +10120,13 @@
       <c r="BI111" s="24"/>
     </row>
     <row r="112" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A112" s="98"/>
-      <c r="B112" s="101"/>
+      <c r="A112" s="110"/>
+      <c r="B112" s="113"/>
       <c r="C112" s="44" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="24"/>
@@ -10189,15 +10189,15 @@
       <c r="BI112" s="24"/>
     </row>
     <row r="113" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A113" s="98"/>
+      <c r="A113" s="110"/>
       <c r="B113" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="C113" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="D113" s="22" t="s">
         <v>311</v>
-      </c>
-      <c r="C113" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="D113" s="22" t="s">
-        <v>313</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="24"/>
@@ -10260,15 +10260,15 @@
       <c r="BI113" s="24"/>
     </row>
     <row r="114" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A114" s="98"/>
-      <c r="B114" s="88" t="s">
+      <c r="A114" s="110"/>
+      <c r="B114" s="100" t="s">
+        <v>312</v>
+      </c>
+      <c r="C114" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="D114" s="22" t="s">
         <v>314</v>
-      </c>
-      <c r="C114" s="44" t="s">
-        <v>315</v>
-      </c>
-      <c r="D114" s="22" t="s">
-        <v>316</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="24"/>
@@ -10331,13 +10331,13 @@
       <c r="BI114" s="24"/>
     </row>
     <row r="115" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A115" s="98"/>
-      <c r="B115" s="90"/>
+      <c r="A115" s="110"/>
+      <c r="B115" s="102"/>
       <c r="C115" s="44" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D115" s="47" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E115" s="23"/>
       <c r="F115" s="24"/>
@@ -10400,15 +10400,15 @@
       <c r="BI115" s="24"/>
     </row>
     <row r="116" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A116" s="97"/>
+      <c r="A116" s="109"/>
       <c r="B116" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="C116" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="D116" s="22" t="s">
         <v>319</v>
-      </c>
-      <c r="C116" s="44" t="s">
-        <v>320</v>
-      </c>
-      <c r="D116" s="22" t="s">
-        <v>321</v>
       </c>
       <c r="E116" s="23"/>
       <c r="F116" s="24"/>
@@ -10471,18 +10471,18 @@
       <c r="BI116" s="24"/>
     </row>
     <row r="118" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B118" s="102" t="s">
-        <v>322</v>
-      </c>
-      <c r="C118" s="102"/>
-      <c r="D118" s="102"/>
-      <c r="E118" s="102"/>
-      <c r="F118" s="102"/>
-      <c r="G118" s="102"/>
-      <c r="H118" s="102"/>
-      <c r="I118" s="102"/>
-      <c r="J118" s="102"/>
-      <c r="K118" s="102"/>
+      <c r="B118" s="114" t="s">
+        <v>320</v>
+      </c>
+      <c r="C118" s="114"/>
+      <c r="D118" s="114"/>
+      <c r="E118" s="114"/>
+      <c r="F118" s="114"/>
+      <c r="G118" s="114"/>
+      <c r="H118" s="114"/>
+      <c r="I118" s="114"/>
+      <c r="J118" s="114"/>
+      <c r="K118" s="114"/>
       <c r="L118" s="48"/>
       <c r="M118" s="48"/>
       <c r="N118" s="48"/>
@@ -10502,50 +10502,50 @@
       <c r="AB118" s="48"/>
     </row>
     <row r="119" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B119" s="103" t="s">
+      <c r="B119" s="115" t="s">
+        <v>321</v>
+      </c>
+      <c r="C119" s="115"/>
+      <c r="D119" s="115"/>
+      <c r="E119" s="115"/>
+      <c r="F119" s="115"/>
+      <c r="G119" s="115"/>
+      <c r="H119" s="115"/>
+      <c r="I119" s="115"/>
+      <c r="J119" s="115"/>
+      <c r="K119" s="115"/>
+    </row>
+    <row r="120" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="B120" s="116" t="s">
+        <v>322</v>
+      </c>
+      <c r="C120" s="116"/>
+      <c r="D120" s="116"/>
+      <c r="E120" s="116"/>
+      <c r="F120" s="116"/>
+      <c r="G120" s="116"/>
+      <c r="H120" s="116"/>
+      <c r="I120" s="116"/>
+      <c r="J120" s="116"/>
+      <c r="K120" s="116"/>
+    </row>
+    <row r="121" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="B121" s="117" t="s">
         <v>323</v>
       </c>
-      <c r="C119" s="103"/>
-      <c r="D119" s="103"/>
-      <c r="E119" s="103"/>
-      <c r="F119" s="103"/>
-      <c r="G119" s="103"/>
-      <c r="H119" s="103"/>
-      <c r="I119" s="103"/>
-      <c r="J119" s="103"/>
-      <c r="K119" s="103"/>
-    </row>
-    <row r="120" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B120" s="104" t="s">
-        <v>324</v>
-      </c>
-      <c r="C120" s="104"/>
-      <c r="D120" s="104"/>
-      <c r="E120" s="104"/>
-      <c r="F120" s="104"/>
-      <c r="G120" s="104"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="104"/>
-      <c r="J120" s="104"/>
-      <c r="K120" s="104"/>
-    </row>
-    <row r="121" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B121" s="105" t="s">
-        <v>325</v>
-      </c>
-      <c r="C121" s="105"/>
-      <c r="D121" s="105"/>
-      <c r="E121" s="105"/>
-      <c r="F121" s="105"/>
-      <c r="G121" s="105"/>
-      <c r="H121" s="105"/>
-      <c r="I121" s="105"/>
-      <c r="J121" s="105"/>
-      <c r="K121" s="105"/>
+      <c r="C121" s="117"/>
+      <c r="D121" s="117"/>
+      <c r="E121" s="117"/>
+      <c r="F121" s="117"/>
+      <c r="G121" s="117"/>
+      <c r="H121" s="117"/>
+      <c r="I121" s="117"/>
+      <c r="J121" s="117"/>
+      <c r="K121" s="117"/>
     </row>
     <row r="123" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -10641,115 +10641,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="91"/>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="68" t="s">
+      <c r="A1" s="103"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="68" t="s">
+      <c r="S1" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="68" t="s">
+      <c r="W1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="76" t="s">
+      <c r="AE1" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
-      <c r="AH1" s="77"/>
-      <c r="AI1" s="77"/>
-      <c r="AJ1" s="77"/>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
-      <c r="AN1" s="77"/>
-      <c r="AO1" s="78"/>
+      <c r="AF1" s="89"/>
+      <c r="AG1" s="89"/>
+      <c r="AH1" s="89"/>
+      <c r="AI1" s="89"/>
+      <c r="AJ1" s="89"/>
+      <c r="AK1" s="89"/>
+      <c r="AL1" s="89"/>
+      <c r="AM1" s="89"/>
+      <c r="AN1" s="89"/>
+      <c r="AO1" s="90"/>
       <c r="AP1" s="1"/>
-      <c r="AQ1" s="79" t="s">
+      <c r="AQ1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="80"/>
-      <c r="AS1" s="80"/>
-      <c r="AT1" s="81"/>
+      <c r="AR1" s="92"/>
+      <c r="AS1" s="92"/>
+      <c r="AT1" s="93"/>
       <c r="AU1" s="1"/>
-      <c r="AV1" s="68" t="s">
+      <c r="AV1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="AW1" s="68"/>
-      <c r="AX1" s="68"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
       <c r="AY1" s="1"/>
-      <c r="AZ1" s="65" t="s">
+      <c r="AZ1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="BA1" s="66"/>
-      <c r="BB1" s="66"/>
-      <c r="BC1" s="66"/>
+      <c r="BA1" s="77"/>
+      <c r="BB1" s="77"/>
+      <c r="BC1" s="77"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="BF1" s="1"/>
-      <c r="BG1" s="68" t="s">
+      <c r="BG1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="BH1" s="68"/>
-      <c r="BI1" s="68"/>
+      <c r="BH1" s="79"/>
+      <c r="BI1" s="79"/>
     </row>
     <row r="2" spans="1:61" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="91"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="106">
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="118">
         <v>1</v>
       </c>
-      <c r="F2" s="106"/>
+      <c r="F2" s="118"/>
       <c r="G2" s="49">
         <v>2</v>
       </c>
       <c r="H2" s="49">
         <v>3</v>
       </c>
-      <c r="I2" s="106">
+      <c r="I2" s="118">
         <v>4</v>
       </c>
-      <c r="J2" s="106"/>
+      <c r="J2" s="118"/>
       <c r="K2" s="49">
         <v>5</v>
       </c>
       <c r="L2" s="49">
         <v>6</v>
       </c>
-      <c r="M2" s="106">
+      <c r="M2" s="118">
         <v>7</v>
       </c>
-      <c r="N2" s="106"/>
+      <c r="N2" s="118"/>
       <c r="O2" s="49">
         <v>8</v>
       </c>
@@ -10760,10 +10760,10 @@
         <v>10</v>
       </c>
       <c r="R2" s="5"/>
-      <c r="S2" s="106">
+      <c r="S2" s="118">
         <v>1</v>
       </c>
-      <c r="T2" s="106"/>
+      <c r="T2" s="118"/>
       <c r="U2" s="49">
         <v>2</v>
       </c>
@@ -10777,11 +10777,11 @@
       <c r="Y2" s="49">
         <v>3</v>
       </c>
-      <c r="Z2" s="106">
+      <c r="Z2" s="118">
         <v>4</v>
       </c>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
       <c r="AC2" s="49">
         <v>5</v>
       </c>
@@ -10871,10 +10871,10 @@
       </c>
     </row>
     <row r="3" spans="1:61" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="91"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="92"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="49">
         <v>1</v>
       </c>
@@ -11032,10 +11032,10 @@
       </c>
     </row>
     <row r="4" spans="1:61" s="20" customFormat="1" ht="329" x14ac:dyDescent="0.2">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="92"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
       <c r="E4" s="16" t="s">
         <v>10</v>
       </c>
@@ -11077,129 +11077,129 @@
       </c>
       <c r="R4" s="18"/>
       <c r="S4" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="U4" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U4" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="V4" s="18"/>
       <c r="W4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="19" t="s">
+      <c r="Z4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="19" t="s">
+      <c r="AA4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="19" t="s">
+      <c r="AB4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AC4" s="19" t="s">
         <v>30</v>
-      </c>
-      <c r="AB4" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC4" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="AD4" s="18"/>
       <c r="AE4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AF4" s="19" t="s">
+      <c r="AH4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AG4" s="19" t="s">
+      <c r="AI4" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="19" t="s">
+      <c r="AK4" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AJ4" s="19" t="s">
+      <c r="AL4" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="19" t="s">
+      <c r="AM4" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AL4" s="19" t="s">
+      <c r="AN4" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AM4" s="19" t="s">
+      <c r="AO4" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="AN4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO4" s="19" t="s">
-        <v>43</v>
       </c>
       <c r="AP4" s="18"/>
       <c r="AQ4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS4" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AR4" s="19" t="s">
+      <c r="AT4" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="AS4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT4" s="19" t="s">
-        <v>47</v>
       </c>
       <c r="AU4" s="18"/>
       <c r="AV4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AW4" s="19" t="s">
+      <c r="AY4" s="18"/>
+      <c r="AZ4" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="AX4" s="19" t="s">
+      <c r="BA4" s="106"/>
+      <c r="BB4" s="107"/>
+      <c r="BC4" s="50" t="s">
         <v>50</v>
-      </c>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="94" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA4" s="94"/>
-      <c r="BB4" s="95"/>
-      <c r="BC4" s="50" t="s">
-        <v>52</v>
       </c>
       <c r="BD4" s="18"/>
       <c r="BE4" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="BF4" s="18"/>
       <c r="BG4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="BH4" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="BI4" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="BH4" s="19" t="s">
+    </row>
+    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A5" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="BI4" s="19" t="s">
+      <c r="B5" s="119" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A5" s="82" t="s">
+      <c r="C5" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="118" t="s">
+      <c r="D5" s="22" t="s">
         <v>58</v>
-      </c>
-      <c r="C5" s="119" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>60</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="24"/>
@@ -11260,13 +11260,13 @@
       <c r="BI5" s="25"/>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A6" s="83"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="120"/>
-      <c r="C6" s="119" t="s">
-        <v>61</v>
+      <c r="C6" s="65" t="s">
+        <v>59</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="24"/>
@@ -11327,13 +11327,13 @@
       <c r="BI6" s="25"/>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A7" s="83"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="120"/>
-      <c r="C7" s="121" t="s">
-        <v>63</v>
+      <c r="C7" s="66" t="s">
+        <v>61</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
@@ -11394,13 +11394,13 @@
       <c r="BI7" s="25"/>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A8" s="83"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="120"/>
-      <c r="C8" s="119" t="s">
-        <v>65</v>
+      <c r="C8" s="65" t="s">
+        <v>63</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="24"/>
@@ -11461,13 +11461,13 @@
       <c r="BI8" s="25"/>
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A9" s="83"/>
+      <c r="A9" s="95"/>
       <c r="B9" s="120"/>
-      <c r="C9" s="119" t="s">
-        <v>67</v>
+      <c r="C9" s="65" t="s">
+        <v>65</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
@@ -11528,13 +11528,13 @@
       <c r="BI9" s="25"/>
     </row>
     <row r="10" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A10" s="83"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="120"/>
-      <c r="C10" s="119" t="s">
-        <v>69</v>
+      <c r="C10" s="65" t="s">
+        <v>67</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
@@ -11595,13 +11595,13 @@
       <c r="BI10" s="24"/>
     </row>
     <row r="11" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A11" s="83"/>
+      <c r="A11" s="95"/>
       <c r="B11" s="120"/>
-      <c r="C11" s="121" t="s">
-        <v>71</v>
+      <c r="C11" s="66" t="s">
+        <v>69</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
@@ -11662,13 +11662,13 @@
       <c r="BI11" s="24"/>
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A12" s="83"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="120"/>
-      <c r="C12" s="119" t="s">
-        <v>73</v>
+      <c r="C12" s="65" t="s">
+        <v>71</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="24"/>
@@ -11729,13 +11729,13 @@
       <c r="BI12" s="24"/>
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A13" s="83"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="119" t="s">
-        <v>75</v>
+      <c r="A13" s="95"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="65" t="s">
+        <v>73</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
@@ -11796,15 +11796,15 @@
       <c r="BI13" s="25"/>
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A14" s="83"/>
-      <c r="B14" s="118" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>71</v>
+      <c r="A14" s="95"/>
+      <c r="B14" s="119" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>69</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
@@ -11865,13 +11865,13 @@
       <c r="BI14" s="24"/>
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A15" s="83"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="119" t="s">
-        <v>73</v>
+      <c r="A15" s="95"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="65" t="s">
+        <v>71</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
@@ -11932,15 +11932,15 @@
       <c r="BI15" s="24"/>
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A16" s="83"/>
-      <c r="B16" s="118" t="s">
+      <c r="A16" s="95"/>
+      <c r="B16" s="119" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>78</v>
-      </c>
-      <c r="C16" s="119" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>80</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
@@ -12001,13 +12001,13 @@
       <c r="BI16" s="24"/>
     </row>
     <row r="17" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A17" s="83"/>
+      <c r="A17" s="95"/>
       <c r="B17" s="120"/>
-      <c r="C17" s="119" t="s">
-        <v>81</v>
+      <c r="C17" s="65" t="s">
+        <v>79</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -12068,15 +12068,15 @@
       <c r="BI17" s="24"/>
     </row>
     <row r="18" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A18" s="83"/>
-      <c r="B18" s="123" t="s">
+      <c r="A18" s="95"/>
+      <c r="B18" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="C18" s="124" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>85</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -12137,15 +12137,15 @@
       <c r="BI18" s="24"/>
     </row>
     <row r="19" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A19" s="84"/>
-      <c r="B19" s="125" t="s">
+      <c r="A19" s="96"/>
+      <c r="B19" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>86</v>
-      </c>
-      <c r="C19" s="119" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>88</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -12206,17 +12206,17 @@
       <c r="BI19" s="24"/>
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="119" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="118" t="s">
+      <c r="D20" s="22" t="s">
         <v>90</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>92</v>
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
@@ -12277,13 +12277,13 @@
       <c r="BI20" s="24"/>
     </row>
     <row r="21" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A21" s="83"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="120"/>
-      <c r="C21" s="119" t="s">
-        <v>93</v>
+      <c r="C21" s="65" t="s">
+        <v>91</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
@@ -12344,13 +12344,13 @@
       <c r="BI21" s="24"/>
     </row>
     <row r="22" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A22" s="83"/>
+      <c r="A22" s="95"/>
       <c r="B22" s="120"/>
-      <c r="C22" s="119" t="s">
-        <v>95</v>
+      <c r="C22" s="65" t="s">
+        <v>93</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
@@ -12411,13 +12411,13 @@
       <c r="BI22" s="24"/>
     </row>
     <row r="23" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A23" s="83"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="120"/>
-      <c r="C23" s="121" t="s">
+      <c r="C23" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>95</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>97</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
@@ -12478,13 +12478,13 @@
       <c r="BI23" s="24"/>
     </row>
     <row r="24" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A24" s="83"/>
+      <c r="A24" s="95"/>
       <c r="B24" s="120"/>
-      <c r="C24" s="119" t="s">
-        <v>98</v>
+      <c r="C24" s="65" t="s">
+        <v>96</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
@@ -12545,13 +12545,13 @@
       <c r="BI24" s="24"/>
     </row>
     <row r="25" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A25" s="83"/>
+      <c r="A25" s="95"/>
       <c r="B25" s="120"/>
-      <c r="C25" s="119" t="s">
-        <v>100</v>
+      <c r="C25" s="65" t="s">
+        <v>98</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
@@ -12612,13 +12612,13 @@
       <c r="BI25" s="24"/>
     </row>
     <row r="26" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A26" s="83"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="120"/>
-      <c r="C26" s="119" t="s">
-        <v>102</v>
+      <c r="C26" s="65" t="s">
+        <v>100</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -12679,13 +12679,13 @@
       <c r="BI26" s="24"/>
     </row>
     <row r="27" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A27" s="83"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="120"/>
-      <c r="C27" s="119" t="s">
-        <v>104</v>
+      <c r="C27" s="65" t="s">
+        <v>102</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="24"/>
@@ -12746,13 +12746,13 @@
       <c r="BI27" s="24"/>
     </row>
     <row r="28" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A28" s="83"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="120"/>
-      <c r="C28" s="119" t="s">
-        <v>106</v>
+      <c r="C28" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E28" s="23"/>
       <c r="F28" s="24"/>
@@ -12813,13 +12813,13 @@
       <c r="BI28" s="24"/>
     </row>
     <row r="29" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A29" s="83"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="120"/>
-      <c r="C29" s="119" t="s">
-        <v>108</v>
+      <c r="C29" s="65" t="s">
+        <v>106</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="24"/>
@@ -12880,13 +12880,13 @@
       <c r="BI29" s="24"/>
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A30" s="83"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="120"/>
-      <c r="C30" s="119" t="s">
-        <v>110</v>
+      <c r="C30" s="65" t="s">
+        <v>108</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E30" s="23"/>
       <c r="F30" s="24"/>
@@ -12947,13 +12947,13 @@
       <c r="BI30" s="24"/>
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A31" s="83"/>
+      <c r="A31" s="95"/>
       <c r="B31" s="120"/>
-      <c r="C31" s="119" t="s">
-        <v>112</v>
+      <c r="C31" s="65" t="s">
+        <v>110</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E31" s="23"/>
       <c r="F31" s="24"/>
@@ -13014,13 +13014,13 @@
       <c r="BI31" s="24"/>
     </row>
     <row r="32" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A32" s="83"/>
+      <c r="A32" s="95"/>
       <c r="B32" s="120"/>
-      <c r="C32" s="119" t="s">
-        <v>114</v>
+      <c r="C32" s="65" t="s">
+        <v>112</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" s="23"/>
       <c r="F32" s="24"/>
@@ -13081,13 +13081,13 @@
       <c r="BI32" s="24"/>
     </row>
     <row r="33" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A33" s="83"/>
+      <c r="A33" s="95"/>
       <c r="B33" s="120"/>
-      <c r="C33" s="119" t="s">
-        <v>116</v>
+      <c r="C33" s="65" t="s">
+        <v>114</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E33" s="23"/>
       <c r="F33" s="24"/>
@@ -13148,13 +13148,13 @@
       <c r="BI33" s="24"/>
     </row>
     <row r="34" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A34" s="83"/>
+      <c r="A34" s="95"/>
       <c r="B34" s="120"/>
-      <c r="C34" s="119" t="s">
-        <v>118</v>
+      <c r="C34" s="65" t="s">
+        <v>116</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E34" s="23"/>
       <c r="F34" s="24"/>
@@ -13215,13 +13215,13 @@
       <c r="BI34" s="24"/>
     </row>
     <row r="35" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A35" s="83"/>
+      <c r="A35" s="95"/>
       <c r="B35" s="120"/>
-      <c r="C35" s="119" t="s">
-        <v>120</v>
+      <c r="C35" s="65" t="s">
+        <v>118</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E35" s="23"/>
       <c r="F35" s="24"/>
@@ -13282,13 +13282,13 @@
       <c r="BI35" s="24"/>
     </row>
     <row r="36" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A36" s="83"/>
+      <c r="A36" s="95"/>
       <c r="B36" s="120"/>
-      <c r="C36" s="119" t="s">
-        <v>122</v>
+      <c r="C36" s="65" t="s">
+        <v>120</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E36" s="23"/>
       <c r="F36" s="24"/>
@@ -13349,13 +13349,13 @@
       <c r="BI36" s="24"/>
     </row>
     <row r="37" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A37" s="83"/>
+      <c r="A37" s="95"/>
       <c r="B37" s="120"/>
-      <c r="C37" s="119" t="s">
-        <v>124</v>
+      <c r="C37" s="65" t="s">
+        <v>122</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -13416,13 +13416,13 @@
       <c r="BI37" s="24"/>
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A38" s="83"/>
+      <c r="A38" s="95"/>
       <c r="B38" s="120"/>
-      <c r="C38" s="119" t="s">
-        <v>126</v>
+      <c r="C38" s="65" t="s">
+        <v>124</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E38" s="23"/>
       <c r="F38" s="24"/>
@@ -13483,13 +13483,13 @@
       <c r="BI38" s="24"/>
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A39" s="83"/>
-      <c r="B39" s="122"/>
-      <c r="C39" s="119" t="s">
-        <v>128</v>
+      <c r="A39" s="95"/>
+      <c r="B39" s="121"/>
+      <c r="C39" s="65" t="s">
+        <v>126</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="24"/>
@@ -13550,15 +13550,15 @@
       <c r="BI39" s="24"/>
     </row>
     <row r="40" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A40" s="83"/>
-      <c r="B40" s="126" t="s">
+      <c r="A40" s="95"/>
+      <c r="B40" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="22" t="s">
         <v>130</v>
-      </c>
-      <c r="C40" s="119" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>132</v>
       </c>
       <c r="E40" s="23"/>
       <c r="F40" s="24"/>
@@ -13619,15 +13619,15 @@
       <c r="BI40" s="24"/>
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A41" s="83"/>
-      <c r="B41" s="127" t="s">
+      <c r="A41" s="95"/>
+      <c r="B41" s="122" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="C41" s="124" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>135</v>
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
@@ -13688,13 +13688,13 @@
       <c r="BI41" s="24"/>
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A42" s="83"/>
-      <c r="B42" s="128"/>
-      <c r="C42" s="124" t="s">
-        <v>136</v>
+      <c r="A42" s="95"/>
+      <c r="B42" s="123"/>
+      <c r="C42" s="68" t="s">
+        <v>134</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E42" s="23"/>
       <c r="F42" s="24"/>
@@ -13755,13 +13755,13 @@
       <c r="BI42" s="24"/>
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A43" s="83"/>
-      <c r="B43" s="128"/>
-      <c r="C43" s="124" t="s">
-        <v>138</v>
+      <c r="A43" s="95"/>
+      <c r="B43" s="123"/>
+      <c r="C43" s="68" t="s">
+        <v>136</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -13822,13 +13822,13 @@
       <c r="BI43" s="24"/>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A44" s="83"/>
-      <c r="B44" s="128"/>
-      <c r="C44" s="124" t="s">
-        <v>140</v>
+      <c r="A44" s="95"/>
+      <c r="B44" s="123"/>
+      <c r="C44" s="68" t="s">
+        <v>138</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E44" s="23"/>
       <c r="F44" s="24"/>
@@ -13889,13 +13889,13 @@
       <c r="BI44" s="24"/>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A45" s="83"/>
-      <c r="B45" s="128"/>
-      <c r="C45" s="124" t="s">
-        <v>142</v>
+      <c r="A45" s="95"/>
+      <c r="B45" s="123"/>
+      <c r="C45" s="68" t="s">
+        <v>140</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="24"/>
@@ -13956,13 +13956,13 @@
       <c r="BI45" s="24"/>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A46" s="83"/>
-      <c r="B46" s="128"/>
-      <c r="C46" s="124" t="s">
-        <v>144</v>
+      <c r="A46" s="95"/>
+      <c r="B46" s="123"/>
+      <c r="C46" s="68" t="s">
+        <v>142</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E46" s="23"/>
       <c r="F46" s="24"/>
@@ -14023,13 +14023,13 @@
       <c r="BI46" s="24"/>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A47" s="83"/>
-      <c r="B47" s="128"/>
-      <c r="C47" s="124" t="s">
-        <v>146</v>
+      <c r="A47" s="95"/>
+      <c r="B47" s="123"/>
+      <c r="C47" s="68" t="s">
+        <v>144</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E47" s="23"/>
       <c r="F47" s="24"/>
@@ -14090,13 +14090,13 @@
       <c r="BI47" s="24"/>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A48" s="83"/>
-      <c r="B48" s="129"/>
-      <c r="C48" s="124" t="s">
-        <v>148</v>
+      <c r="A48" s="95"/>
+      <c r="B48" s="124"/>
+      <c r="C48" s="68" t="s">
+        <v>146</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -14157,15 +14157,15 @@
       <c r="BI48" s="24"/>
     </row>
     <row r="49" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A49" s="83"/>
-      <c r="B49" s="127" t="s">
+      <c r="A49" s="95"/>
+      <c r="B49" s="122" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>150</v>
-      </c>
-      <c r="C49" s="124" t="s">
-        <v>151</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>152</v>
       </c>
       <c r="E49" s="23"/>
       <c r="F49" s="24"/>
@@ -14226,13 +14226,13 @@
       <c r="BI49" s="24"/>
     </row>
     <row r="50" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A50" s="84"/>
-      <c r="B50" s="129"/>
-      <c r="C50" s="124" t="s">
-        <v>153</v>
+      <c r="A50" s="96"/>
+      <c r="B50" s="124"/>
+      <c r="C50" s="68" t="s">
+        <v>151</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E50" s="23"/>
       <c r="F50" s="24"/>
@@ -14356,17 +14356,17 @@
       <c r="BI51" s="26"/>
     </row>
     <row r="52" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="108" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="125" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="B52" s="130" t="s">
+      <c r="D52" s="22" t="s">
         <v>156</v>
-      </c>
-      <c r="C52" s="124" t="s">
-        <v>157</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>158</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -14427,13 +14427,13 @@
       <c r="BI52" s="24"/>
     </row>
     <row r="53" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A53" s="98"/>
-      <c r="B53" s="131"/>
-      <c r="C53" s="124" t="s">
-        <v>159</v>
+      <c r="A53" s="110"/>
+      <c r="B53" s="126"/>
+      <c r="C53" s="68" t="s">
+        <v>157</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E53" s="23"/>
       <c r="F53" s="24"/>
@@ -14494,15 +14494,15 @@
       <c r="BI53" s="24"/>
     </row>
     <row r="54" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A54" s="98"/>
-      <c r="B54" s="132" t="s">
+      <c r="A54" s="110"/>
+      <c r="B54" s="71" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="22" t="s">
         <v>161</v>
-      </c>
-      <c r="C54" s="119" t="s">
-        <v>162</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>163</v>
       </c>
       <c r="E54" s="23"/>
       <c r="F54" s="24"/>
@@ -14563,15 +14563,15 @@
       <c r="BI54" s="24"/>
     </row>
     <row r="55" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A55" s="98"/>
-      <c r="B55" s="127" t="s">
+      <c r="A55" s="110"/>
+      <c r="B55" s="122" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="22" t="s">
         <v>164</v>
-      </c>
-      <c r="C55" s="124" t="s">
-        <v>165</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>166</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="24"/>
@@ -14632,13 +14632,13 @@
       <c r="BI55" s="24"/>
     </row>
     <row r="56" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A56" s="98"/>
-      <c r="B56" s="128"/>
-      <c r="C56" s="124" t="s">
-        <v>167</v>
+      <c r="A56" s="110"/>
+      <c r="B56" s="123"/>
+      <c r="C56" s="68" t="s">
+        <v>165</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="24"/>
@@ -14699,13 +14699,13 @@
       <c r="BI56" s="24"/>
     </row>
     <row r="57" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A57" s="97"/>
-      <c r="B57" s="129"/>
-      <c r="C57" s="124" t="s">
-        <v>169</v>
+      <c r="A57" s="109"/>
+      <c r="B57" s="124"/>
+      <c r="C57" s="68" t="s">
+        <v>167</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="24"/>
@@ -14829,17 +14829,17 @@
       <c r="BI58" s="26"/>
     </row>
     <row r="59" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A59" s="96" t="s">
+      <c r="A59" s="108" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="72" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="68" t="s">
         <v>171</v>
       </c>
-      <c r="B59" s="133" t="s">
+      <c r="D59" s="22" t="s">
         <v>172</v>
-      </c>
-      <c r="C59" s="124" t="s">
-        <v>173</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>174</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="24"/>
@@ -14900,15 +14900,15 @@
       <c r="BI59" s="24"/>
     </row>
     <row r="60" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A60" s="98"/>
-      <c r="B60" s="133" t="s">
+      <c r="A60" s="110"/>
+      <c r="B60" s="72" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="22" t="s">
         <v>175</v>
-      </c>
-      <c r="C60" s="124" t="s">
-        <v>176</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>177</v>
       </c>
       <c r="E60" s="23"/>
       <c r="F60" s="24"/>
@@ -14969,15 +14969,15 @@
       <c r="BI60" s="24"/>
     </row>
     <row r="61" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A61" s="98"/>
-      <c r="B61" s="133" t="s">
+      <c r="A61" s="110"/>
+      <c r="B61" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="22" t="s">
         <v>178</v>
-      </c>
-      <c r="C61" s="124" t="s">
-        <v>179</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>180</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="24"/>
@@ -15038,15 +15038,15 @@
       <c r="BI61" s="24"/>
     </row>
     <row r="62" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A62" s="98"/>
-      <c r="B62" s="133" t="s">
+      <c r="A62" s="110"/>
+      <c r="B62" s="72" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" s="22" t="s">
         <v>181</v>
-      </c>
-      <c r="C62" s="124" t="s">
-        <v>182</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>183</v>
       </c>
       <c r="E62" s="23"/>
       <c r="F62" s="24"/>
@@ -15107,15 +15107,15 @@
       <c r="BI62" s="24"/>
     </row>
     <row r="63" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A63" s="98"/>
-      <c r="B63" s="127" t="s">
+      <c r="A63" s="110"/>
+      <c r="B63" s="122" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" s="22" t="s">
         <v>184</v>
-      </c>
-      <c r="C63" s="124" t="s">
-        <v>185</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>186</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="24"/>
@@ -15176,13 +15176,13 @@
       <c r="BI63" s="24"/>
     </row>
     <row r="64" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A64" s="98"/>
-      <c r="B64" s="129"/>
-      <c r="C64" s="124" t="s">
-        <v>187</v>
+      <c r="A64" s="110"/>
+      <c r="B64" s="124"/>
+      <c r="C64" s="68" t="s">
+        <v>185</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="24"/>
@@ -15243,15 +15243,15 @@
       <c r="BI64" s="24"/>
     </row>
     <row r="65" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A65" s="98"/>
-      <c r="B65" s="133" t="s">
+      <c r="A65" s="110"/>
+      <c r="B65" s="72" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="D65" s="22" t="s">
         <v>189</v>
-      </c>
-      <c r="C65" s="124" t="s">
-        <v>190</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>191</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="24"/>
@@ -15312,15 +15312,15 @@
       <c r="BI65" s="24"/>
     </row>
     <row r="66" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A66" s="97"/>
-      <c r="B66" s="134" t="s">
+      <c r="A66" s="109"/>
+      <c r="B66" s="73" t="s">
+        <v>190</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="22" t="s">
         <v>192</v>
-      </c>
-      <c r="C66" s="124" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>194</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="24"/>
@@ -15444,17 +15444,17 @@
       <c r="BI67" s="26"/>
     </row>
     <row r="68" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A68" s="96" t="s">
+      <c r="A68" s="108" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="127" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="B68" s="135" t="s">
+      <c r="D68" s="22" t="s">
         <v>196</v>
-      </c>
-      <c r="C68" s="124" t="s">
-        <v>197</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>198</v>
       </c>
       <c r="E68" s="23"/>
       <c r="F68" s="24"/>
@@ -15515,13 +15515,13 @@
       <c r="BI68" s="24"/>
     </row>
     <row r="69" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A69" s="98"/>
-      <c r="B69" s="135"/>
-      <c r="C69" s="124" t="s">
-        <v>199</v>
+      <c r="A69" s="110"/>
+      <c r="B69" s="127"/>
+      <c r="C69" s="68" t="s">
+        <v>197</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E69" s="23"/>
       <c r="F69" s="24"/>
@@ -15582,15 +15582,15 @@
       <c r="BI69" s="24"/>
     </row>
     <row r="70" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A70" s="98"/>
-      <c r="B70" s="135" t="s">
+      <c r="A70" s="110"/>
+      <c r="B70" s="127" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" s="22" t="s">
         <v>201</v>
-      </c>
-      <c r="C70" s="124" t="s">
-        <v>202</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>203</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="24"/>
@@ -15651,13 +15651,13 @@
       <c r="BI70" s="24"/>
     </row>
     <row r="71" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A71" s="98"/>
-      <c r="B71" s="135"/>
-      <c r="C71" s="124" t="s">
-        <v>204</v>
+      <c r="A71" s="110"/>
+      <c r="B71" s="127"/>
+      <c r="C71" s="68" t="s">
+        <v>202</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E71" s="23"/>
       <c r="F71" s="24"/>
@@ -15718,15 +15718,15 @@
       <c r="BI71" s="24"/>
     </row>
     <row r="72" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A72" s="98"/>
-      <c r="B72" s="133" t="s">
+      <c r="A72" s="110"/>
+      <c r="B72" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="C72" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72" s="22" t="s">
         <v>206</v>
-      </c>
-      <c r="C72" s="124" t="s">
-        <v>207</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>208</v>
       </c>
       <c r="E72" s="23"/>
       <c r="F72" s="24"/>
@@ -15787,15 +15787,15 @@
       <c r="BI72" s="24"/>
     </row>
     <row r="73" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A73" s="98"/>
-      <c r="B73" s="133" t="s">
+      <c r="A73" s="110"/>
+      <c r="B73" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="D73" s="22" t="s">
         <v>209</v>
-      </c>
-      <c r="C73" s="124" t="s">
-        <v>210</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>211</v>
       </c>
       <c r="E73" s="23"/>
       <c r="F73" s="24"/>
@@ -15856,15 +15856,15 @@
       <c r="BI73" s="24"/>
     </row>
     <row r="74" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A74" s="98"/>
-      <c r="B74" s="133" t="s">
+      <c r="A74" s="110"/>
+      <c r="B74" s="72" t="s">
+        <v>210</v>
+      </c>
+      <c r="C74" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="D74" s="22" t="s">
         <v>212</v>
-      </c>
-      <c r="C74" s="124" t="s">
-        <v>213</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>214</v>
       </c>
       <c r="E74" s="23"/>
       <c r="F74" s="24"/>
@@ -15925,15 +15925,15 @@
       <c r="BI74" s="24"/>
     </row>
     <row r="75" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A75" s="98"/>
-      <c r="B75" s="135" t="s">
+      <c r="A75" s="110"/>
+      <c r="B75" s="127" t="s">
+        <v>213</v>
+      </c>
+      <c r="C75" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="D75" s="22" t="s">
         <v>215</v>
-      </c>
-      <c r="C75" s="136" t="s">
-        <v>216</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="24"/>
@@ -15994,13 +15994,13 @@
       <c r="BI75" s="24"/>
     </row>
     <row r="76" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A76" s="98"/>
-      <c r="B76" s="135"/>
-      <c r="C76" s="136" t="s">
-        <v>218</v>
+      <c r="A76" s="110"/>
+      <c r="B76" s="127"/>
+      <c r="C76" s="74" t="s">
+        <v>216</v>
       </c>
       <c r="D76" s="22" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
@@ -16061,13 +16061,13 @@
       <c r="BI76" s="24"/>
     </row>
     <row r="77" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A77" s="98"/>
-      <c r="B77" s="135"/>
-      <c r="C77" s="136" t="s">
-        <v>220</v>
+      <c r="A77" s="110"/>
+      <c r="B77" s="127"/>
+      <c r="C77" s="74" t="s">
+        <v>218</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="24"/>
@@ -16128,15 +16128,15 @@
       <c r="BI77" s="24"/>
     </row>
     <row r="78" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A78" s="97"/>
-      <c r="B78" s="137" t="s">
+      <c r="A78" s="109"/>
+      <c r="B78" s="75" t="s">
+        <v>220</v>
+      </c>
+      <c r="C78" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="D78" s="22" t="s">
         <v>222</v>
-      </c>
-      <c r="C78" s="136" t="s">
-        <v>223</v>
-      </c>
-      <c r="D78" s="22" t="s">
-        <v>224</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="24"/>
@@ -16197,17 +16197,17 @@
       <c r="BI78" s="24"/>
     </row>
     <row r="79" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A79" s="96" t="s">
+      <c r="A79" s="108" t="s">
+        <v>223</v>
+      </c>
+      <c r="B79" s="122" t="s">
+        <v>224</v>
+      </c>
+      <c r="C79" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="B79" s="127" t="s">
+      <c r="D79" s="22" t="s">
         <v>226</v>
-      </c>
-      <c r="C79" s="124" t="s">
-        <v>227</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>228</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="24"/>
@@ -16268,13 +16268,13 @@
       <c r="BI79" s="24"/>
     </row>
     <row r="80" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A80" s="98"/>
-      <c r="B80" s="129"/>
-      <c r="C80" s="124" t="s">
-        <v>229</v>
+      <c r="A80" s="110"/>
+      <c r="B80" s="124"/>
+      <c r="C80" s="68" t="s">
+        <v>227</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E80" s="23"/>
       <c r="F80" s="24"/>
@@ -16335,15 +16335,15 @@
       <c r="BI80" s="24"/>
     </row>
     <row r="81" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A81" s="98"/>
-      <c r="B81" s="123" t="s">
+      <c r="A81" s="110"/>
+      <c r="B81" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="D81" s="22" t="s">
         <v>231</v>
-      </c>
-      <c r="C81" s="124" t="s">
-        <v>232</v>
-      </c>
-      <c r="D81" s="22" t="s">
-        <v>233</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="24"/>
@@ -16404,15 +16404,15 @@
       <c r="BI81" s="24"/>
     </row>
     <row r="82" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A82" s="98"/>
-      <c r="B82" s="135" t="s">
+      <c r="A82" s="110"/>
+      <c r="B82" s="127" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" s="74" t="s">
+        <v>233</v>
+      </c>
+      <c r="D82" s="22" t="s">
         <v>234</v>
-      </c>
-      <c r="C82" s="136" t="s">
-        <v>235</v>
-      </c>
-      <c r="D82" s="22" t="s">
-        <v>236</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="24"/>
@@ -16473,13 +16473,13 @@
       <c r="BI82" s="24"/>
     </row>
     <row r="83" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A83" s="98"/>
-      <c r="B83" s="135"/>
-      <c r="C83" s="136" t="s">
-        <v>237</v>
+      <c r="A83" s="110"/>
+      <c r="B83" s="127"/>
+      <c r="C83" s="74" t="s">
+        <v>235</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="24"/>
@@ -16540,15 +16540,15 @@
       <c r="BI83" s="24"/>
     </row>
     <row r="84" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A84" s="98"/>
-      <c r="B84" s="137" t="s">
+      <c r="A84" s="110"/>
+      <c r="B84" s="75" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" s="74" t="s">
+        <v>238</v>
+      </c>
+      <c r="D84" s="22" t="s">
         <v>239</v>
-      </c>
-      <c r="C84" s="136" t="s">
-        <v>240</v>
-      </c>
-      <c r="D84" s="22" t="s">
-        <v>241</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="24"/>
@@ -16609,15 +16609,15 @@
       <c r="BI84" s="24"/>
     </row>
     <row r="85" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A85" s="98"/>
-      <c r="B85" s="127" t="s">
+      <c r="A85" s="110"/>
+      <c r="B85" s="122" t="s">
+        <v>240</v>
+      </c>
+      <c r="C85" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="22" t="s">
         <v>242</v>
-      </c>
-      <c r="C85" s="136" t="s">
-        <v>243</v>
-      </c>
-      <c r="D85" s="22" t="s">
-        <v>244</v>
       </c>
       <c r="E85" s="23"/>
       <c r="F85" s="24"/>
@@ -16678,13 +16678,13 @@
       <c r="BI85" s="24"/>
     </row>
     <row r="86" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A86" s="98"/>
-      <c r="B86" s="128"/>
-      <c r="C86" s="136" t="s">
-        <v>245</v>
+      <c r="A86" s="110"/>
+      <c r="B86" s="123"/>
+      <c r="C86" s="74" t="s">
+        <v>243</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E86" s="23"/>
       <c r="F86" s="24"/>
@@ -16745,13 +16745,13 @@
       <c r="BI86" s="24"/>
     </row>
     <row r="87" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A87" s="98"/>
-      <c r="B87" s="129"/>
-      <c r="C87" s="136" t="s">
-        <v>247</v>
+      <c r="A87" s="110"/>
+      <c r="B87" s="124"/>
+      <c r="C87" s="74" t="s">
+        <v>245</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="24"/>
@@ -16812,15 +16812,15 @@
       <c r="BI87" s="24"/>
     </row>
     <row r="88" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A88" s="98"/>
-      <c r="B88" s="137" t="s">
+      <c r="A88" s="110"/>
+      <c r="B88" s="75" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" s="74" t="s">
+        <v>248</v>
+      </c>
+      <c r="D88" s="22" t="s">
         <v>249</v>
-      </c>
-      <c r="C88" s="136" t="s">
-        <v>250</v>
-      </c>
-      <c r="D88" s="22" t="s">
-        <v>251</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="24"/>
@@ -16881,15 +16881,15 @@
       <c r="BI88" s="24"/>
     </row>
     <row r="89" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A89" s="98"/>
-      <c r="B89" s="127" t="s">
+      <c r="A89" s="110"/>
+      <c r="B89" s="122" t="s">
+        <v>250</v>
+      </c>
+      <c r="C89" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="22" t="s">
         <v>252</v>
-      </c>
-      <c r="C89" s="136" t="s">
-        <v>253</v>
-      </c>
-      <c r="D89" s="22" t="s">
-        <v>254</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="24"/>
@@ -16950,13 +16950,13 @@
       <c r="BI89" s="24"/>
     </row>
     <row r="90" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A90" s="98"/>
-      <c r="B90" s="128"/>
-      <c r="C90" s="136" t="s">
-        <v>255</v>
+      <c r="A90" s="110"/>
+      <c r="B90" s="123"/>
+      <c r="C90" s="74" t="s">
+        <v>253</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="24"/>
@@ -17017,13 +17017,13 @@
       <c r="BI90" s="24"/>
     </row>
     <row r="91" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A91" s="98"/>
-      <c r="B91" s="128"/>
-      <c r="C91" s="136" t="s">
-        <v>245</v>
+      <c r="A91" s="110"/>
+      <c r="B91" s="123"/>
+      <c r="C91" s="74" t="s">
+        <v>243</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
@@ -17084,13 +17084,13 @@
       <c r="BI91" s="24"/>
     </row>
     <row r="92" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A92" s="97"/>
-      <c r="B92" s="129"/>
-      <c r="C92" s="136" t="s">
-        <v>247</v>
+      <c r="A92" s="109"/>
+      <c r="B92" s="124"/>
+      <c r="C92" s="74" t="s">
+        <v>245</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="24"/>
@@ -17151,17 +17151,17 @@
       <c r="BI92" s="24"/>
     </row>
     <row r="93" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A93" s="96" t="s">
+      <c r="A93" s="108" t="s">
+        <v>255</v>
+      </c>
+      <c r="B93" s="122" t="s">
+        <v>256</v>
+      </c>
+      <c r="C93" s="74" t="s">
         <v>257</v>
       </c>
-      <c r="B93" s="127" t="s">
+      <c r="D93" s="22" t="s">
         <v>258</v>
-      </c>
-      <c r="C93" s="136" t="s">
-        <v>259</v>
-      </c>
-      <c r="D93" s="22" t="s">
-        <v>260</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="24"/>
@@ -17222,13 +17222,13 @@
       <c r="BI93" s="24"/>
     </row>
     <row r="94" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A94" s="97"/>
-      <c r="B94" s="129"/>
-      <c r="C94" s="136" t="s">
-        <v>261</v>
+      <c r="A94" s="109"/>
+      <c r="B94" s="124"/>
+      <c r="C94" s="74" t="s">
+        <v>259</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
@@ -17352,17 +17352,17 @@
       <c r="BI95" s="26"/>
     </row>
     <row r="96" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A96" s="96" t="s">
+      <c r="A96" s="108" t="s">
+        <v>261</v>
+      </c>
+      <c r="B96" s="127" t="s">
+        <v>262</v>
+      </c>
+      <c r="C96" s="74" t="s">
         <v>263</v>
       </c>
-      <c r="B96" s="135" t="s">
+      <c r="D96" s="22" t="s">
         <v>264</v>
-      </c>
-      <c r="C96" s="136" t="s">
-        <v>265</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>266</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="24"/>
@@ -17423,13 +17423,13 @@
       <c r="BI96" s="24"/>
     </row>
     <row r="97" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A97" s="98"/>
-      <c r="B97" s="135"/>
-      <c r="C97" s="136" t="s">
-        <v>267</v>
+      <c r="A97" s="110"/>
+      <c r="B97" s="127"/>
+      <c r="C97" s="74" t="s">
+        <v>265</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="24"/>
@@ -17490,15 +17490,15 @@
       <c r="BI97" s="24"/>
     </row>
     <row r="98" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="97"/>
-      <c r="B98" s="134" t="s">
+      <c r="A98" s="109"/>
+      <c r="B98" s="73" t="s">
+        <v>267</v>
+      </c>
+      <c r="C98" s="74" t="s">
+        <v>268</v>
+      </c>
+      <c r="D98" s="22" t="s">
         <v>269</v>
-      </c>
-      <c r="C98" s="136" t="s">
-        <v>270</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>271</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="24"/>
@@ -17558,17 +17558,17 @@
       <c r="BI98" s="24"/>
     </row>
     <row r="99" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A99" s="96" t="s">
+      <c r="A99" s="108" t="s">
+        <v>270</v>
+      </c>
+      <c r="B99" s="75" t="s">
+        <v>271</v>
+      </c>
+      <c r="C99" s="74" t="s">
         <v>272</v>
       </c>
-      <c r="B99" s="137" t="s">
+      <c r="D99" s="22" t="s">
         <v>273</v>
-      </c>
-      <c r="C99" s="136" t="s">
-        <v>274</v>
-      </c>
-      <c r="D99" s="22" t="s">
-        <v>275</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="24"/>
@@ -17629,15 +17629,15 @@
       <c r="BI99" s="24"/>
     </row>
     <row r="100" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A100" s="98"/>
-      <c r="B100" s="134" t="s">
+      <c r="A100" s="110"/>
+      <c r="B100" s="73" t="s">
+        <v>274</v>
+      </c>
+      <c r="C100" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="D100" s="22" t="s">
         <v>276</v>
-      </c>
-      <c r="C100" s="136" t="s">
-        <v>277</v>
-      </c>
-      <c r="D100" s="22" t="s">
-        <v>278</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="24"/>
@@ -17698,15 +17698,15 @@
       <c r="BI100" s="24"/>
     </row>
     <row r="101" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="97"/>
-      <c r="B101" s="134" t="s">
+      <c r="A101" s="109"/>
+      <c r="B101" s="73" t="s">
+        <v>277</v>
+      </c>
+      <c r="C101" s="74" t="s">
+        <v>278</v>
+      </c>
+      <c r="D101" s="46" t="s">
         <v>279</v>
-      </c>
-      <c r="C101" s="136" t="s">
-        <v>280</v>
-      </c>
-      <c r="D101" s="46" t="s">
-        <v>281</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="24"/>
@@ -17767,17 +17767,17 @@
       <c r="BI101" s="24"/>
     </row>
     <row r="102" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="96" t="s">
+      <c r="A102" s="108" t="s">
+        <v>280</v>
+      </c>
+      <c r="B102" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="C102" s="74" t="s">
         <v>282</v>
       </c>
-      <c r="B102" s="133" t="s">
+      <c r="D102" s="46" t="s">
         <v>283</v>
-      </c>
-      <c r="C102" s="136" t="s">
-        <v>284</v>
-      </c>
-      <c r="D102" s="46" t="s">
-        <v>285</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="24"/>
@@ -17838,15 +17838,15 @@
       <c r="BI102" s="24"/>
     </row>
     <row r="103" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A103" s="97"/>
-      <c r="B103" s="134" t="s">
+      <c r="A103" s="109"/>
+      <c r="B103" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="74" t="s">
+        <v>285</v>
+      </c>
+      <c r="D103" s="22" t="s">
         <v>286</v>
-      </c>
-      <c r="C103" s="136" t="s">
-        <v>287</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>288</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="24"/>
@@ -17970,17 +17970,17 @@
       <c r="BI104" s="26"/>
     </row>
     <row r="105" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A105" s="96" t="s">
+      <c r="A105" s="108" t="s">
+        <v>287</v>
+      </c>
+      <c r="B105" s="72" t="s">
+        <v>288</v>
+      </c>
+      <c r="C105" s="68" t="s">
         <v>289</v>
       </c>
-      <c r="B105" s="133" t="s">
+      <c r="D105" s="22" t="s">
         <v>290</v>
-      </c>
-      <c r="C105" s="124" t="s">
-        <v>291</v>
-      </c>
-      <c r="D105" s="22" t="s">
-        <v>292</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="24"/>
@@ -18041,15 +18041,15 @@
       <c r="BI105" s="24"/>
     </row>
     <row r="106" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A106" s="98"/>
-      <c r="B106" s="133" t="s">
+      <c r="A106" s="110"/>
+      <c r="B106" s="72" t="s">
+        <v>291</v>
+      </c>
+      <c r="C106" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="D106" s="22" t="s">
         <v>293</v>
-      </c>
-      <c r="C106" s="124" t="s">
-        <v>294</v>
-      </c>
-      <c r="D106" s="22" t="s">
-        <v>295</v>
       </c>
       <c r="E106" s="23"/>
       <c r="F106" s="24"/>
@@ -18110,15 +18110,15 @@
       <c r="BI106" s="24"/>
     </row>
     <row r="107" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A107" s="98"/>
-      <c r="B107" s="133" t="s">
+      <c r="A107" s="110"/>
+      <c r="B107" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="C107" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="D107" s="22" t="s">
         <v>296</v>
-      </c>
-      <c r="C107" s="124" t="s">
-        <v>297</v>
-      </c>
-      <c r="D107" s="22" t="s">
-        <v>298</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="24"/>
@@ -18179,15 +18179,15 @@
       <c r="BI107" s="24"/>
     </row>
     <row r="108" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A108" s="98"/>
-      <c r="B108" s="135" t="s">
+      <c r="A108" s="110"/>
+      <c r="B108" s="127" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" s="74" t="s">
+        <v>298</v>
+      </c>
+      <c r="D108" s="22" t="s">
         <v>299</v>
-      </c>
-      <c r="C108" s="136" t="s">
-        <v>300</v>
-      </c>
-      <c r="D108" s="22" t="s">
-        <v>301</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="24"/>
@@ -18248,13 +18248,13 @@
       <c r="BI108" s="24"/>
     </row>
     <row r="109" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A109" s="98"/>
-      <c r="B109" s="135"/>
-      <c r="C109" s="136" t="s">
-        <v>302</v>
+      <c r="A109" s="110"/>
+      <c r="B109" s="127"/>
+      <c r="C109" s="74" t="s">
+        <v>300</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E109" s="23"/>
       <c r="F109" s="24"/>
@@ -18315,13 +18315,13 @@
       <c r="BI109" s="24"/>
     </row>
     <row r="110" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A110" s="98"/>
-      <c r="B110" s="135"/>
-      <c r="C110" s="136" t="s">
-        <v>304</v>
+      <c r="A110" s="110"/>
+      <c r="B110" s="127"/>
+      <c r="C110" s="74" t="s">
+        <v>302</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="24"/>
@@ -18382,15 +18382,15 @@
       <c r="BI110" s="24"/>
     </row>
     <row r="111" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A111" s="98"/>
-      <c r="B111" s="135" t="s">
+      <c r="A111" s="110"/>
+      <c r="B111" s="127" t="s">
+        <v>304</v>
+      </c>
+      <c r="C111" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="D111" s="22" t="s">
         <v>306</v>
-      </c>
-      <c r="C111" s="136" t="s">
-        <v>307</v>
-      </c>
-      <c r="D111" s="22" t="s">
-        <v>308</v>
       </c>
       <c r="E111" s="23"/>
       <c r="F111" s="24"/>
@@ -18451,13 +18451,13 @@
       <c r="BI111" s="24"/>
     </row>
     <row r="112" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A112" s="98"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136" t="s">
-        <v>309</v>
+      <c r="A112" s="110"/>
+      <c r="B112" s="127"/>
+      <c r="C112" s="74" t="s">
+        <v>307</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="24"/>
@@ -18518,15 +18518,15 @@
       <c r="BI112" s="24"/>
     </row>
     <row r="113" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A113" s="98"/>
-      <c r="B113" s="133" t="s">
+      <c r="A113" s="110"/>
+      <c r="B113" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="C113" s="74" t="s">
+        <v>310</v>
+      </c>
+      <c r="D113" s="22" t="s">
         <v>311</v>
-      </c>
-      <c r="C113" s="136" t="s">
-        <v>312</v>
-      </c>
-      <c r="D113" s="22" t="s">
-        <v>313</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="24"/>
@@ -18587,15 +18587,15 @@
       <c r="BI113" s="24"/>
     </row>
     <row r="114" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A114" s="98"/>
-      <c r="B114" s="127" t="s">
+      <c r="A114" s="110"/>
+      <c r="B114" s="122" t="s">
+        <v>312</v>
+      </c>
+      <c r="C114" s="74" t="s">
+        <v>313</v>
+      </c>
+      <c r="D114" s="22" t="s">
         <v>314</v>
-      </c>
-      <c r="C114" s="136" t="s">
-        <v>315</v>
-      </c>
-      <c r="D114" s="22" t="s">
-        <v>316</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="24"/>
@@ -18656,13 +18656,13 @@
       <c r="BI114" s="24"/>
     </row>
     <row r="115" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A115" s="98"/>
-      <c r="B115" s="129"/>
-      <c r="C115" s="136" t="s">
-        <v>317</v>
+      <c r="A115" s="110"/>
+      <c r="B115" s="124"/>
+      <c r="C115" s="74" t="s">
+        <v>315</v>
       </c>
       <c r="D115" s="47" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E115" s="23"/>
       <c r="F115" s="24"/>
@@ -18723,15 +18723,15 @@
       <c r="BI115" s="24"/>
     </row>
     <row r="116" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A116" s="97"/>
-      <c r="B116" s="133" t="s">
+      <c r="A116" s="109"/>
+      <c r="B116" s="72" t="s">
+        <v>317</v>
+      </c>
+      <c r="C116" s="74" t="s">
+        <v>318</v>
+      </c>
+      <c r="D116" s="22" t="s">
         <v>319</v>
-      </c>
-      <c r="C116" s="136" t="s">
-        <v>320</v>
-      </c>
-      <c r="D116" s="22" t="s">
-        <v>321</v>
       </c>
       <c r="E116" s="23"/>
       <c r="F116" s="24"/>
@@ -18792,18 +18792,18 @@
       <c r="BI116" s="24"/>
     </row>
     <row r="118" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B118" s="102" t="s">
-        <v>322</v>
-      </c>
-      <c r="C118" s="102"/>
-      <c r="D118" s="102"/>
-      <c r="E118" s="102"/>
-      <c r="F118" s="102"/>
-      <c r="G118" s="102"/>
-      <c r="H118" s="102"/>
-      <c r="I118" s="102"/>
-      <c r="J118" s="102"/>
-      <c r="K118" s="102"/>
+      <c r="B118" s="114" t="s">
+        <v>320</v>
+      </c>
+      <c r="C118" s="114"/>
+      <c r="D118" s="114"/>
+      <c r="E118" s="114"/>
+      <c r="F118" s="114"/>
+      <c r="G118" s="114"/>
+      <c r="H118" s="114"/>
+      <c r="I118" s="114"/>
+      <c r="J118" s="114"/>
+      <c r="K118" s="114"/>
       <c r="L118" s="48"/>
       <c r="M118" s="48"/>
       <c r="N118" s="48"/>
@@ -18823,46 +18823,46 @@
       <c r="AB118" s="48"/>
     </row>
     <row r="119" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B119" s="103" t="s">
+      <c r="B119" s="115" t="s">
+        <v>321</v>
+      </c>
+      <c r="C119" s="115"/>
+      <c r="D119" s="115"/>
+      <c r="E119" s="115"/>
+      <c r="F119" s="115"/>
+      <c r="G119" s="115"/>
+      <c r="H119" s="115"/>
+      <c r="I119" s="115"/>
+      <c r="J119" s="115"/>
+      <c r="K119" s="115"/>
+    </row>
+    <row r="120" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="B120" s="116" t="s">
+        <v>332</v>
+      </c>
+      <c r="C120" s="116"/>
+      <c r="D120" s="116"/>
+      <c r="E120" s="116"/>
+      <c r="F120" s="116"/>
+      <c r="G120" s="116"/>
+      <c r="H120" s="116"/>
+      <c r="I120" s="116"/>
+      <c r="J120" s="116"/>
+      <c r="K120" s="116"/>
+    </row>
+    <row r="121" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="B121" s="128" t="s">
         <v>323</v>
       </c>
-      <c r="C119" s="103"/>
-      <c r="D119" s="103"/>
-      <c r="E119" s="103"/>
-      <c r="F119" s="103"/>
-      <c r="G119" s="103"/>
-      <c r="H119" s="103"/>
-      <c r="I119" s="103"/>
-      <c r="J119" s="103"/>
-      <c r="K119" s="103"/>
-    </row>
-    <row r="120" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B120" s="104" t="s">
-        <v>334</v>
-      </c>
-      <c r="C120" s="104"/>
-      <c r="D120" s="104"/>
-      <c r="E120" s="104"/>
-      <c r="F120" s="104"/>
-      <c r="G120" s="104"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="104"/>
-      <c r="J120" s="104"/>
-      <c r="K120" s="104"/>
-    </row>
-    <row r="121" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="B121" s="107" t="s">
-        <v>325</v>
-      </c>
-      <c r="C121" s="105"/>
-      <c r="D121" s="105"/>
-      <c r="E121" s="105"/>
-      <c r="F121" s="105"/>
-      <c r="G121" s="105"/>
-      <c r="H121" s="105"/>
-      <c r="I121" s="105"/>
-      <c r="J121" s="105"/>
-      <c r="K121" s="105"/>
+      <c r="C121" s="117"/>
+      <c r="D121" s="117"/>
+      <c r="E121" s="117"/>
+      <c r="F121" s="117"/>
+      <c r="G121" s="117"/>
+      <c r="H121" s="117"/>
+      <c r="I121" s="117"/>
+      <c r="J121" s="117"/>
+      <c r="K121" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="51">
@@ -18953,119 +18953,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="118"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
       <c r="D1" s="64" t="s">
-        <v>326</v>
-      </c>
-      <c r="E1" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="E1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="68" t="s">
+      <c r="S1" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="68" t="s">
+      <c r="W1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="76" t="s">
+      <c r="AE1" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
-      <c r="AH1" s="77"/>
-      <c r="AI1" s="77"/>
-      <c r="AJ1" s="77"/>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
-      <c r="AN1" s="77"/>
-      <c r="AO1" s="78"/>
+      <c r="AF1" s="89"/>
+      <c r="AG1" s="89"/>
+      <c r="AH1" s="89"/>
+      <c r="AI1" s="89"/>
+      <c r="AJ1" s="89"/>
+      <c r="AK1" s="89"/>
+      <c r="AL1" s="89"/>
+      <c r="AM1" s="89"/>
+      <c r="AN1" s="89"/>
+      <c r="AO1" s="90"/>
       <c r="AP1" s="1"/>
-      <c r="AQ1" s="79" t="s">
+      <c r="AQ1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="80"/>
-      <c r="AS1" s="80"/>
-      <c r="AT1" s="81"/>
+      <c r="AR1" s="92"/>
+      <c r="AS1" s="92"/>
+      <c r="AT1" s="93"/>
       <c r="AU1" s="1"/>
-      <c r="AV1" s="68" t="s">
+      <c r="AV1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="AW1" s="68"/>
-      <c r="AX1" s="68"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="79"/>
       <c r="AY1" s="1"/>
-      <c r="AZ1" s="65" t="s">
+      <c r="AZ1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="BA1" s="66"/>
-      <c r="BB1" s="66"/>
-      <c r="BC1" s="66"/>
+      <c r="BA1" s="77"/>
+      <c r="BB1" s="77"/>
+      <c r="BC1" s="77"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="BF1" s="1"/>
-      <c r="BG1" s="68" t="s">
+      <c r="BG1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="BH1" s="68"/>
-      <c r="BI1" s="68"/>
+      <c r="BH1" s="79"/>
+      <c r="BI1" s="79"/>
     </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
       <c r="D2" s="64" t="s">
-        <v>330</v>
-      </c>
-      <c r="E2" s="106">
+        <v>328</v>
+      </c>
+      <c r="E2" s="118">
         <v>1</v>
       </c>
-      <c r="F2" s="106"/>
+      <c r="F2" s="118"/>
       <c r="G2" s="49">
         <v>2</v>
       </c>
       <c r="H2" s="49">
         <v>3</v>
       </c>
-      <c r="I2" s="106">
+      <c r="I2" s="118">
         <v>4</v>
       </c>
-      <c r="J2" s="106"/>
+      <c r="J2" s="118"/>
       <c r="K2" s="49">
         <v>5</v>
       </c>
       <c r="L2" s="49">
         <v>6</v>
       </c>
-      <c r="M2" s="106">
+      <c r="M2" s="118">
         <v>7</v>
       </c>
-      <c r="N2" s="106"/>
+      <c r="N2" s="118"/>
       <c r="O2" s="49">
         <v>8</v>
       </c>
@@ -19076,10 +19076,10 @@
         <v>10</v>
       </c>
       <c r="R2" s="5"/>
-      <c r="S2" s="106">
+      <c r="S2" s="118">
         <v>1</v>
       </c>
-      <c r="T2" s="106"/>
+      <c r="T2" s="118"/>
       <c r="U2" s="49">
         <v>2</v>
       </c>
@@ -19093,11 +19093,11 @@
       <c r="Y2" s="49">
         <v>3</v>
       </c>
-      <c r="Z2" s="106">
+      <c r="Z2" s="118">
         <v>4</v>
       </c>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
       <c r="AC2" s="49">
         <v>5</v>
       </c>
@@ -19187,11 +19187,11 @@
       </c>
     </row>
     <row r="3" spans="1:61" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="106"/>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="118"/>
       <c r="D3" s="64" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E3" s="49">
         <v>1</v>
@@ -19351,16 +19351,16 @@
     </row>
     <row r="4" spans="1:61" ht="329" x14ac:dyDescent="0.2">
       <c r="A4" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="D4" s="53" t="s">
         <v>327</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>328</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>329</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>10</v>
@@ -19403,122 +19403,122 @@
       </c>
       <c r="R4" s="18"/>
       <c r="S4" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="U4" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U4" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="V4" s="18"/>
       <c r="W4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="19" t="s">
+      <c r="Z4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="19" t="s">
+      <c r="AA4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="19" t="s">
+      <c r="AB4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AC4" s="19" t="s">
         <v>30</v>
-      </c>
-      <c r="AB4" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC4" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="AD4" s="18"/>
       <c r="AE4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AF4" s="19" t="s">
+      <c r="AH4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AG4" s="19" t="s">
+      <c r="AI4" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AI4" s="19" t="s">
+      <c r="AK4" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AJ4" s="19" t="s">
+      <c r="AL4" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="19" t="s">
+      <c r="AM4" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AL4" s="19" t="s">
+      <c r="AN4" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AM4" s="19" t="s">
+      <c r="AO4" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="AN4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO4" s="19" t="s">
-        <v>43</v>
       </c>
       <c r="AP4" s="18"/>
       <c r="AQ4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS4" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AR4" s="19" t="s">
+      <c r="AT4" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="AS4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT4" s="19" t="s">
-        <v>47</v>
       </c>
       <c r="AU4" s="18"/>
       <c r="AV4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AW4" s="19" t="s">
+      <c r="AY4" s="18"/>
+      <c r="AZ4" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="AX4" s="19" t="s">
+      <c r="BA4" s="106"/>
+      <c r="BB4" s="107"/>
+      <c r="BC4" s="50" t="s">
         <v>50</v>
-      </c>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="94" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA4" s="94"/>
-      <c r="BB4" s="95"/>
-      <c r="BC4" s="50" t="s">
-        <v>52</v>
       </c>
       <c r="BD4" s="18"/>
       <c r="BE4" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="BF4" s="18"/>
       <c r="BG4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="BH4" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="BI4" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="BH4" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="BI4" s="19" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="5" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="130">
         <v>1</v>
       </c>
       <c r="C5" s="24">
@@ -19586,8 +19586,8 @@
       <c r="BI5" s="25"/>
     </row>
     <row r="6" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
+      <c r="A6" s="129"/>
+      <c r="B6" s="130"/>
       <c r="C6" s="24">
         <v>2</v>
       </c>
@@ -19653,7 +19653,7 @@
       <c r="BI6" s="25"/>
     </row>
     <row r="7" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="108"/>
+      <c r="A7" s="129"/>
       <c r="B7" s="24">
         <v>2</v>
       </c>
@@ -19722,7 +19722,7 @@
       <c r="BI7" s="25"/>
     </row>
     <row r="8" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="108"/>
+      <c r="A8" s="129"/>
       <c r="B8" s="24">
         <v>3</v>
       </c>
@@ -19791,8 +19791,8 @@
       <c r="BI8" s="25"/>
     </row>
     <row r="9" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
-      <c r="B9" s="109">
+      <c r="A9" s="129"/>
+      <c r="B9" s="130">
         <v>4</v>
       </c>
       <c r="C9" s="24">
@@ -19860,8 +19860,8 @@
       <c r="BI9" s="25"/>
     </row>
     <row r="10" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="108"/>
-      <c r="B10" s="109"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="130"/>
       <c r="C10" s="24">
         <v>2</v>
       </c>
@@ -19927,7 +19927,7 @@
       <c r="BI10" s="24"/>
     </row>
     <row r="11" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="108"/>
+      <c r="A11" s="129"/>
       <c r="B11" s="24">
         <v>5</v>
       </c>
@@ -19996,7 +19996,7 @@
       <c r="BI11" s="24"/>
     </row>
     <row r="12" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="108"/>
+      <c r="A12" s="129"/>
       <c r="B12" s="24">
         <v>6</v>
       </c>
@@ -20065,8 +20065,8 @@
       <c r="BI12" s="24"/>
     </row>
     <row r="13" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="108"/>
-      <c r="B13" s="109">
+      <c r="A13" s="129"/>
+      <c r="B13" s="130">
         <v>7</v>
       </c>
       <c r="C13" s="24">
@@ -20134,8 +20134,8 @@
       <c r="BI13" s="25"/>
     </row>
     <row r="14" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="108"/>
-      <c r="B14" s="109"/>
+      <c r="A14" s="129"/>
+      <c r="B14" s="130"/>
       <c r="C14" s="24">
         <v>2</v>
       </c>
@@ -20201,7 +20201,7 @@
       <c r="BI14" s="24"/>
     </row>
     <row r="15" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
+      <c r="A15" s="129"/>
       <c r="B15" s="24">
         <v>8</v>
       </c>
@@ -20270,7 +20270,7 @@
       <c r="BI15" s="24"/>
     </row>
     <row r="16" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="108"/>
+      <c r="A16" s="129"/>
       <c r="B16" s="24">
         <v>9</v>
       </c>
@@ -20339,7 +20339,7 @@
       <c r="BI16" s="24"/>
     </row>
     <row r="17" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+      <c r="A17" s="129"/>
       <c r="B17" s="24">
         <v>10</v>
       </c>
@@ -20471,17 +20471,17 @@
       <c r="BI18" s="58"/>
     </row>
     <row r="19" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="109">
+      <c r="B19" s="130">
         <v>1</v>
       </c>
       <c r="C19" s="24">
         <v>1</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>23</v>
+        <v>334</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -20542,13 +20542,13 @@
       <c r="BI19" s="24"/>
     </row>
     <row r="20" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="108"/>
-      <c r="B20" s="109"/>
+      <c r="A20" s="129"/>
+      <c r="B20" s="130"/>
       <c r="C20" s="24">
         <v>2</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>24</v>
+        <v>335</v>
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
@@ -20609,7 +20609,7 @@
       <c r="BI20" s="24"/>
     </row>
     <row r="21" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="108"/>
+      <c r="A21" s="129"/>
       <c r="B21" s="24">
         <v>2</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="54" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
@@ -20741,7 +20741,7 @@
       <c r="BI22" s="58"/>
     </row>
     <row r="23" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="108" t="s">
+      <c r="A23" s="129" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="24">
@@ -20751,7 +20751,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
@@ -20812,7 +20812,7 @@
       <c r="BI23" s="24"/>
     </row>
     <row r="24" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="108"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="24">
         <v>2</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
@@ -20881,7 +20881,7 @@
       <c r="BI24" s="24"/>
     </row>
     <row r="25" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="108"/>
+      <c r="A25" s="129"/>
       <c r="B25" s="24">
         <v>3</v>
       </c>
@@ -20889,7 +20889,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
@@ -20950,15 +20950,15 @@
       <c r="BI25" s="24"/>
     </row>
     <row r="26" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="108"/>
-      <c r="B26" s="109">
+      <c r="A26" s="129"/>
+      <c r="B26" s="130">
         <v>4</v>
       </c>
       <c r="C26" s="24">
         <v>1</v>
       </c>
       <c r="D26" s="59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
@@ -21019,13 +21019,13 @@
       <c r="BI26" s="24"/>
     </row>
     <row r="27" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
+      <c r="A27" s="129"/>
+      <c r="B27" s="130"/>
       <c r="C27" s="24">
         <v>2</v>
       </c>
       <c r="D27" s="59" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="24"/>
@@ -21086,13 +21086,13 @@
       <c r="BI27" s="24"/>
     </row>
     <row r="28" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="108"/>
-      <c r="B28" s="109"/>
+      <c r="A28" s="129"/>
+      <c r="B28" s="130"/>
       <c r="C28" s="24">
         <v>3</v>
       </c>
       <c r="D28" s="59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E28" s="23"/>
       <c r="F28" s="24"/>
@@ -21153,7 +21153,7 @@
       <c r="BI28" s="24"/>
     </row>
     <row r="29" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="108"/>
+      <c r="A29" s="129"/>
       <c r="B29" s="24">
         <v>5</v>
       </c>
@@ -21161,7 +21161,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="24"/>
@@ -21285,7 +21285,7 @@
       <c r="BI30" s="58"/>
     </row>
     <row r="31" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="110" t="s">
+      <c r="A31" s="131" t="s">
         <v>3</v>
       </c>
       <c r="B31" s="24">
@@ -21295,7 +21295,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="59" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E31" s="23"/>
       <c r="F31" s="24"/>
@@ -21356,7 +21356,7 @@
       <c r="BI31" s="24"/>
     </row>
     <row r="32" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="111"/>
+      <c r="A32" s="132"/>
       <c r="B32" s="24">
         <v>2</v>
       </c>
@@ -21364,7 +21364,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E32" s="23"/>
       <c r="F32" s="24"/>
@@ -21425,7 +21425,7 @@
       <c r="BI32" s="24"/>
     </row>
     <row r="33" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="111"/>
+      <c r="A33" s="132"/>
       <c r="B33" s="24">
         <v>3</v>
       </c>
@@ -21433,7 +21433,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E33" s="23"/>
       <c r="F33" s="24"/>
@@ -21494,7 +21494,7 @@
       <c r="BI33" s="24"/>
     </row>
     <row r="34" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="111"/>
+      <c r="A34" s="132"/>
       <c r="B34" s="24">
         <v>4</v>
       </c>
@@ -21502,7 +21502,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E34" s="23"/>
       <c r="F34" s="24"/>
@@ -21563,7 +21563,7 @@
       <c r="BI34" s="24"/>
     </row>
     <row r="35" spans="1:61" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="111"/>
+      <c r="A35" s="132"/>
       <c r="B35" s="24">
         <v>5</v>
       </c>
@@ -21571,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="59" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E35" s="23"/>
       <c r="F35" s="24"/>
@@ -21632,7 +21632,7 @@
       <c r="BI35" s="24"/>
     </row>
     <row r="36" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="111"/>
+      <c r="A36" s="132"/>
       <c r="B36" s="24">
         <v>6</v>
       </c>
@@ -21640,7 +21640,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E36" s="23"/>
       <c r="F36" s="24"/>
@@ -21701,7 +21701,7 @@
       <c r="BI36" s="24"/>
     </row>
     <row r="37" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="111"/>
+      <c r="A37" s="132"/>
       <c r="B37" s="24">
         <v>7</v>
       </c>
@@ -21709,7 +21709,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="59" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -21770,7 +21770,7 @@
       <c r="BI37" s="24"/>
     </row>
     <row r="38" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="111"/>
+      <c r="A38" s="132"/>
       <c r="B38" s="24">
         <v>8</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E38" s="23"/>
       <c r="F38" s="24"/>
@@ -21839,7 +21839,7 @@
       <c r="BI38" s="24"/>
     </row>
     <row r="39" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="111"/>
+      <c r="A39" s="132"/>
       <c r="B39" s="24">
         <v>9</v>
       </c>
@@ -21847,7 +21847,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="24"/>
@@ -21908,7 +21908,7 @@
       <c r="BI39" s="24"/>
     </row>
     <row r="40" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="111"/>
+      <c r="A40" s="132"/>
       <c r="B40" s="24">
         <v>10</v>
       </c>
@@ -21916,7 +21916,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E40" s="23"/>
       <c r="F40" s="24"/>
@@ -21977,7 +21977,7 @@
       <c r="BI40" s="24"/>
     </row>
     <row r="41" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="112"/>
+      <c r="A41" s="133"/>
       <c r="B41" s="24">
         <v>11</v>
       </c>
@@ -21985,7 +21985,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="59" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="24"/>
@@ -22109,7 +22109,7 @@
       <c r="BI42" s="58"/>
     </row>
     <row r="43" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="82" t="s">
+      <c r="A43" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B43" s="24">
@@ -22119,7 +22119,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -22180,7 +22180,7 @@
       <c r="BI43" s="24"/>
     </row>
     <row r="44" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="83"/>
+      <c r="A44" s="95"/>
       <c r="B44" s="24">
         <v>2</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E44" s="23"/>
       <c r="F44" s="24"/>
@@ -22249,7 +22249,7 @@
       <c r="BI44" s="24"/>
     </row>
     <row r="45" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="83"/>
+      <c r="A45" s="95"/>
       <c r="B45" s="24">
         <v>3</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="24"/>
@@ -22318,7 +22318,7 @@
       <c r="BI45" s="24"/>
     </row>
     <row r="46" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="84"/>
+      <c r="A46" s="96"/>
       <c r="B46" s="24">
         <v>4</v>
       </c>
@@ -22326,7 +22326,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E46" s="23"/>
       <c r="F46" s="24"/>
@@ -22450,7 +22450,7 @@
       <c r="BI47" s="58"/>
     </row>
     <row r="48" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="108" t="s">
+      <c r="A48" s="129" t="s">
         <v>5</v>
       </c>
       <c r="B48" s="24">
@@ -22460,7 +22460,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -22521,7 +22521,7 @@
       <c r="BI48" s="24"/>
     </row>
     <row r="49" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="108"/>
+      <c r="A49" s="129"/>
       <c r="B49" s="24">
         <v>2</v>
       </c>
@@ -22529,7 +22529,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E49" s="23"/>
       <c r="F49" s="24"/>
@@ -22590,7 +22590,7 @@
       <c r="BI49" s="24"/>
     </row>
     <row r="50" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="108"/>
+      <c r="A50" s="129"/>
       <c r="B50" s="24">
         <v>3</v>
       </c>
@@ -22598,7 +22598,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="59" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E50" s="23"/>
       <c r="F50" s="24"/>
@@ -22722,7 +22722,7 @@
       <c r="BI51" s="26"/>
     </row>
     <row r="52" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="94" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="24">
@@ -22731,8 +22731,8 @@
       <c r="C52" s="24">
         <v>1</v>
       </c>
-      <c r="D52" s="113" t="s">
-        <v>51</v>
+      <c r="D52" s="134" t="s">
+        <v>49</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -22793,14 +22793,14 @@
       <c r="BI52" s="24"/>
     </row>
     <row r="53" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="83"/>
+      <c r="A53" s="95"/>
       <c r="B53" s="24">
         <v>2</v>
       </c>
       <c r="C53" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="114"/>
+      <c r="D53" s="135"/>
       <c r="E53" s="23"/>
       <c r="F53" s="24"/>
       <c r="G53" s="24"/>
@@ -22860,14 +22860,14 @@
       <c r="BI53" s="24"/>
     </row>
     <row r="54" spans="1:61" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="83"/>
+      <c r="A54" s="95"/>
       <c r="B54" s="24">
         <v>3</v>
       </c>
       <c r="C54" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="115"/>
+      <c r="D54" s="136"/>
       <c r="E54" s="23"/>
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
@@ -22927,7 +22927,7 @@
       <c r="BI54" s="24"/>
     </row>
     <row r="55" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="84"/>
+      <c r="A55" s="96"/>
       <c r="B55" s="24">
         <v>4</v>
       </c>
@@ -22935,7 +22935,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="24"/>
@@ -23069,7 +23069,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="24"/>
@@ -23193,7 +23193,7 @@
       <c r="BI58" s="26"/>
     </row>
     <row r="59" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="108" t="s">
+      <c r="A59" s="129" t="s">
         <v>8</v>
       </c>
       <c r="B59" s="24">
@@ -23203,7 +23203,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="24"/>
@@ -23264,7 +23264,7 @@
       <c r="BI59" s="24"/>
     </row>
     <row r="60" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="108"/>
+      <c r="A60" s="129"/>
       <c r="B60" s="24">
         <v>2</v>
       </c>
@@ -23272,7 +23272,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="59" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E60" s="23"/>
       <c r="F60" s="24"/>
@@ -23333,7 +23333,7 @@
       <c r="BI60" s="24"/>
     </row>
     <row r="61" spans="1:61" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="108"/>
+      <c r="A61" s="129"/>
       <c r="B61" s="24">
         <v>3</v>
       </c>
@@ -23341,7 +23341,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="24"/>
@@ -23402,60 +23402,60 @@
       <c r="BI61" s="24"/>
     </row>
     <row r="63" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="D63" s="116" t="s">
-        <v>322</v>
-      </c>
-      <c r="E63" s="116"/>
-      <c r="F63" s="116"/>
-      <c r="G63" s="116"/>
-      <c r="H63" s="116"/>
-      <c r="I63" s="116"/>
-      <c r="J63" s="116"/>
-      <c r="K63" s="116"/>
-      <c r="L63" s="116"/>
-      <c r="M63" s="116"/>
+      <c r="D63" s="137" t="s">
+        <v>320</v>
+      </c>
+      <c r="E63" s="137"/>
+      <c r="F63" s="137"/>
+      <c r="G63" s="137"/>
+      <c r="H63" s="137"/>
+      <c r="I63" s="137"/>
+      <c r="J63" s="137"/>
+      <c r="K63" s="137"/>
+      <c r="L63" s="137"/>
+      <c r="M63" s="137"/>
     </row>
     <row r="64" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="D64" s="103" t="s">
-        <v>323</v>
-      </c>
-      <c r="E64" s="103"/>
-      <c r="F64" s="103"/>
-      <c r="G64" s="103"/>
-      <c r="H64" s="103"/>
-      <c r="I64" s="103"/>
-      <c r="J64" s="103"/>
-      <c r="K64" s="103"/>
-      <c r="L64" s="103"/>
-      <c r="M64" s="103"/>
+      <c r="D64" s="115" t="s">
+        <v>321</v>
+      </c>
+      <c r="E64" s="115"/>
+      <c r="F64" s="115"/>
+      <c r="G64" s="115"/>
+      <c r="H64" s="115"/>
+      <c r="I64" s="115"/>
+      <c r="J64" s="115"/>
+      <c r="K64" s="115"/>
+      <c r="L64" s="115"/>
+      <c r="M64" s="115"/>
     </row>
     <row r="65" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D65" s="117" t="s">
-        <v>332</v>
-      </c>
-      <c r="E65" s="117"/>
-      <c r="F65" s="117"/>
-      <c r="G65" s="117"/>
-      <c r="H65" s="117"/>
-      <c r="I65" s="117"/>
-      <c r="J65" s="117"/>
-      <c r="K65" s="117"/>
-      <c r="L65" s="117"/>
-      <c r="M65" s="117"/>
+      <c r="D65" s="138" t="s">
+        <v>330</v>
+      </c>
+      <c r="E65" s="138"/>
+      <c r="F65" s="138"/>
+      <c r="G65" s="138"/>
+      <c r="H65" s="138"/>
+      <c r="I65" s="138"/>
+      <c r="J65" s="138"/>
+      <c r="K65" s="138"/>
+      <c r="L65" s="138"/>
+      <c r="M65" s="138"/>
     </row>
     <row r="66" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D66" s="105" t="s">
-        <v>333</v>
-      </c>
-      <c r="E66" s="105"/>
-      <c r="F66" s="105"/>
-      <c r="G66" s="105"/>
-      <c r="H66" s="105"/>
-      <c r="I66" s="105"/>
-      <c r="J66" s="105"/>
-      <c r="K66" s="105"/>
-      <c r="L66" s="105"/>
-      <c r="M66" s="105"/>
+      <c r="D66" s="117" t="s">
+        <v>331</v>
+      </c>
+      <c r="E66" s="117"/>
+      <c r="F66" s="117"/>
+      <c r="G66" s="117"/>
+      <c r="H66" s="117"/>
+      <c r="I66" s="117"/>
+      <c r="J66" s="117"/>
+      <c r="K66" s="117"/>
+      <c r="L66" s="117"/>
+      <c r="M66" s="117"/>
     </row>
     <row r="68" spans="4:28" x14ac:dyDescent="0.2">
       <c r="E68" s="63"/>
